--- a/Data/FlightPlan/FPL_20AUG26.xlsx
+++ b/Data/FlightPlan/FPL_20AUG26.xlsx
@@ -521,6 +521,9 @@
     <t>11:05</t>
   </si>
   <si>
+    <t>09:00</t>
+  </si>
+  <si>
     <t>21:25</t>
   </si>
   <si>
@@ -590,492 +593,489 @@
     <t>12:15</t>
   </si>
   <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>VN-A547</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>VN-A550</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>18:25</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>KMG</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>03:10</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>ZHA</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>TBB</t>
+  </si>
+  <si>
     <t>15:00</t>
   </si>
   <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>02:40</t>
+  </si>
+  <si>
+    <t>03:35</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>VTE</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>20:20</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>23:20</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>05:25</t>
+  </si>
+  <si>
+    <t>VN-A655</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
     <t>17:10</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A547</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>VN-A550</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>18:25</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>KMG</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>03:10</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>ZHA</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>TBB</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
     <t>23:10</t>
   </si>
   <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>02:40</t>
-  </si>
-  <si>
-    <t>03:35</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>VTE</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>20:20</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>23:20</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>05:25</t>
-  </si>
-  <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
     <t>VN-A662</t>
   </si>
   <si>
@@ -1085,34 +1085,58 @@
     <t>VN-A663</t>
   </si>
   <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>VN-A666</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
     <t>FSZ</t>
   </si>
   <si>
-    <t>PXU</t>
-  </si>
-  <si>
     <t>00:20</t>
   </si>
   <si>
     <t>03:55</t>
   </si>
   <si>
-    <t>VN-A666</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>VN-A671</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
   </si>
   <si>
     <t>17:40</t>
@@ -1121,30 +1145,6 @@
     <t>00:25</t>
   </si>
   <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>VN-A671</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
     <t>VN-A683</t>
   </si>
   <si>
@@ -1247,7 +1247,7 @@
     <t>Total Record(s): 409</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 19, 2026 21:54</t>
+    <t xml:space="preserve">Generated on  Aug 20, 2026 00:01</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4294,9 +4294,13 @@
       <c t="s" r="J90" s="7">
         <v>169</v>
       </c>
-      <c r="K90" s="7"/>
+      <c t="s" r="K90" s="7">
+        <v>170</v>
+      </c>
       <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
+      <c t="s" r="M90" s="7">
+        <v>20</v>
+      </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
       <c t="s" r="A91" s="6">
@@ -4358,7 +4362,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4391,7 +4395,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4424,7 +4428,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4436,10 +4440,10 @@
         <v>143</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4457,7 +4461,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4469,7 +4473,7 @@
         <v>111</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>112</v>
@@ -4490,7 +4494,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4502,7 +4506,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>61</v>
@@ -4523,7 +4527,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4538,7 +4542,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4556,7 +4560,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4568,10 +4572,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4604,7 +4608,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4616,7 +4620,7 @@
         <v>153</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J101" s="7">
         <v>75</v>
@@ -4637,7 +4641,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4649,7 +4653,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>103</v>
@@ -4670,7 +4674,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4682,10 +4686,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4703,7 +4707,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4715,10 +4719,10 @@
         <v>38</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4736,7 +4740,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4748,10 +4752,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4769,7 +4773,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4781,10 +4785,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4817,7 +4821,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4826,7 +4830,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>144</v>
@@ -4850,13 +4854,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>16</v>
@@ -4883,7 +4887,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4895,7 +4899,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>28</v>
@@ -4909,14 +4913,14 @@
         <v>13</v>
       </c>
       <c r="B111" s="7">
-        <v>467</v>
+        <v>913</v>
       </c>
       <c t="s" r="C111" s="7">
         <v>14</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -4925,13 +4929,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>193</v>
+        <v>151</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>194</v>
+        <v>55</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4942,26 +4946,26 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>468</v>
+        <v>914</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>162</v>
+        <v>194</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>195</v>
@@ -5045,7 +5049,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5108,7 +5112,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J117" s="7">
         <v>63</v>
@@ -5144,7 +5148,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5177,7 +5181,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5189,7 +5193,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>165</v>
@@ -5210,7 +5214,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5222,10 +5226,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5258,7 +5262,7 @@
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
@@ -5270,7 +5274,7 @@
         <v>145</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="J123" s="7">
         <v>101</v>
@@ -5291,7 +5295,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5306,7 +5310,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5324,7 +5328,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5357,7 +5361,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5390,7 +5394,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5423,7 +5427,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5486,7 +5490,7 @@
         <v>212</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5618,7 +5622,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5894,7 +5898,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>97</v>
@@ -6011,7 +6015,7 @@
         <v>92</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6044,7 +6048,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6290,7 +6294,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6404,7 +6408,7 @@
         <v>233</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6515,7 +6519,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>237</v>
@@ -6695,10 +6699,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6728,7 +6732,7 @@
         <v>243</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J171" s="7">
         <v>215</v>
@@ -7022,10 +7026,10 @@
         <v>252</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7055,7 +7059,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J182" s="7">
         <v>140</v>
@@ -7157,7 +7161,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7190,7 +7194,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7223,7 +7227,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7238,7 +7242,7 @@
         <v>68</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7256,7 +7260,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7265,13 +7269,13 @@
         <v>153</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I189" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7289,13 +7293,13 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>16</v>
@@ -7322,7 +7326,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7331,10 +7335,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J191" s="7">
         <v>86</v>
@@ -7355,22 +7359,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7403,7 +7407,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7415,10 +7419,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7436,7 +7440,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7469,7 +7473,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7478,13 +7482,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7502,19 +7506,19 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>121</v>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7568,7 +7572,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7580,7 +7584,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>97</v>
@@ -7601,7 +7605,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7610,10 +7614,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>119</v>
@@ -7649,7 +7653,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7661,7 +7665,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>235</v>
@@ -7682,7 +7686,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7691,7 +7695,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>25</v>
@@ -7715,13 +7719,13 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>16</v>
@@ -7730,7 +7734,7 @@
         <v>197</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7748,7 +7752,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7763,7 +7767,7 @@
         <v>138</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7781,7 +7785,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7793,7 +7797,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>140</v>
@@ -7814,7 +7818,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7847,7 +7851,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7859,7 +7863,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>244</v>
@@ -7895,7 +7899,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7907,10 +7911,10 @@
         <v>137</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7928,7 +7932,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7961,7 +7965,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7970,13 +7974,13 @@
         <v>94</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7994,13 +7998,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>94</v>
@@ -8009,7 +8013,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8027,7 +8031,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8042,7 +8046,7 @@
         <v>209</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8075,7 +8079,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8087,10 +8091,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8108,7 +8112,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8120,10 +8124,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8141,7 +8145,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8153,10 +8157,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8174,7 +8178,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8207,7 +8211,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8222,7 +8226,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8233,14 +8237,14 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8252,10 +8256,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>218</v>
+        <v>289</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8288,7 +8292,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8300,10 +8304,10 @@
         <v>137</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8321,7 +8325,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8330,13 +8334,13 @@
         <v>137</v>
       </c>
       <c t="s" r="H224" s="8">
+        <v>281</v>
+      </c>
+      <c t="s" r="I224" s="7">
         <v>280</v>
       </c>
-      <c t="s" r="I224" s="7">
-        <v>279</v>
-      </c>
       <c t="s" r="J224" s="7">
-        <v>193</v>
+        <v>253</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8354,22 +8358,22 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>137</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8387,7 +8391,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8420,7 +8424,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8432,10 +8436,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8468,7 +8472,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8501,7 +8505,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8513,7 +8517,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>81</v>
@@ -8534,7 +8538,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8543,7 +8547,7 @@
         <v>24</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>112</v>
@@ -8567,19 +8571,19 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>165</v>
@@ -8600,7 +8604,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8648,7 +8652,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8660,10 +8664,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8681,7 +8685,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8714,7 +8718,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8723,7 +8727,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>42</v>
@@ -8747,22 +8751,22 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
@@ -8780,7 +8784,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -8789,7 +8793,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>29</v>
@@ -8813,13 +8817,13 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>16</v>
@@ -8828,7 +8832,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8861,7 +8865,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8870,10 +8874,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>135</v>
@@ -8894,22 +8898,22 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -8927,7 +8931,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8936,10 +8940,10 @@
         <v>153</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>152</v>
@@ -8960,19 +8964,19 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>57</v>
@@ -8993,7 +8997,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9002,13 +9006,13 @@
         <v>153</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9026,22 +9030,22 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9074,7 +9078,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9083,7 +9087,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H249" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="I249" s="7">
         <v>60</v>
@@ -9107,13 +9111,13 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G250" s="8">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="H250" s="8">
         <v>16</v>
@@ -9140,7 +9144,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9149,7 +9153,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>61</v>
@@ -9173,19 +9177,19 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>230</v>
@@ -9221,7 +9225,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9254,7 +9258,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9287,7 +9291,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9320,7 +9324,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9353,7 +9357,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9386,7 +9390,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9398,7 +9402,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>156</v>
@@ -9419,7 +9423,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9467,7 +9471,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9482,7 +9486,7 @@
         <v>117</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9500,7 +9504,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9533,7 +9537,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9542,13 +9546,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>78</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9566,13 +9570,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>24</v>
@@ -9599,7 +9603,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9611,7 +9615,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>53</v>
@@ -9632,7 +9636,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9644,10 +9648,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9665,7 +9669,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9680,7 +9684,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9698,7 +9702,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9710,7 +9714,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>31</v>
@@ -9746,7 +9750,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9761,7 +9765,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9779,7 +9783,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9788,10 +9792,10 @@
         <v>94</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>82</v>
@@ -9812,13 +9816,13 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>94</v>
@@ -9845,7 +9849,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9860,7 +9864,7 @@
         <v>218</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9878,7 +9882,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9893,7 +9897,7 @@
         <v>239</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9926,22 +9930,22 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9959,7 +9963,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9968,10 +9972,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>141</v>
@@ -9992,13 +9996,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>16</v>
@@ -10007,7 +10011,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10025,7 +10029,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10073,7 +10077,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
@@ -10106,7 +10110,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10118,10 +10122,10 @@
         <v>153</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>205</v>
+        <v>170</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10139,7 +10143,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10154,7 +10158,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10172,7 +10176,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10187,7 +10191,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10205,7 +10209,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10220,7 +10224,7 @@
         <v>103</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10238,7 +10242,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10250,7 +10254,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>56</v>
@@ -10260,49 +10264,49 @@
       <c r="M287" s="7"/>
     </row>
     <row r="288" ht="14.25" customHeight="1">
-      <c t="s" r="A288" s="6">
-        <v>13</v>
-      </c>
-      <c r="B288" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="C288" s="7">
-        <v>14</v>
-      </c>
+      <c r="A288" s="6"/>
+      <c r="B288" s="7"/>
+      <c r="C288" s="7"/>
       <c r="D288" s="7"/>
-      <c t="s" r="E288" s="7">
-        <v>320</v>
-      </c>
-      <c r="F288" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G288" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H288" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I288" s="7">
-        <v>322</v>
-      </c>
-      <c t="s" r="J288" s="7">
-        <v>323</v>
-      </c>
+      <c r="E288" s="7"/>
+      <c r="F288" s="7"/>
+      <c r="G288" s="8"/>
+      <c r="H288" s="8"/>
+      <c r="I288" s="7"/>
+      <c r="J288" s="7"/>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
-      <c r="A289" s="6"/>
-      <c r="B289" s="7"/>
-      <c r="C289" s="7"/>
+      <c t="s" r="A289" s="6">
+        <v>13</v>
+      </c>
+      <c r="B289" s="7">
+        <v>270</v>
+      </c>
+      <c t="s" r="C289" s="7">
+        <v>14</v>
+      </c>
       <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7"/>
-      <c r="G289" s="8"/>
-      <c r="H289" s="8"/>
-      <c r="I289" s="7"/>
-      <c r="J289" s="7"/>
+      <c t="s" r="E289" s="7">
+        <v>324</v>
+      </c>
+      <c r="F289" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G289" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H289" s="8">
+        <v>137</v>
+      </c>
+      <c t="s" r="I289" s="7">
+        <v>264</v>
+      </c>
+      <c t="s" r="J289" s="7">
+        <v>101</v>
+      </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c r="M289" s="7"/>
@@ -10312,7 +10316,7 @@
         <v>13</v>
       </c>
       <c r="B290" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="C290" s="7">
         <v>14</v>
@@ -10325,16 +10329,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>263</v>
+        <v>35</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>101</v>
+        <v>287</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10345,7 +10349,7 @@
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>271</v>
+        <v>634</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
@@ -10358,16 +10362,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>35</v>
+        <v>237</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>286</v>
+        <v>325</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10378,7 +10382,7 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>634</v>
+        <v>1504</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
@@ -10391,16 +10395,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>237</v>
+        <v>102</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>325</v>
+        <v>92</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10411,7 +10415,7 @@
         <v>13</v>
       </c>
       <c r="B293" s="7">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
@@ -10424,16 +10428,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H293" s="8">
         <v>153</v>
       </c>
-      <c t="s" r="H293" s="8">
-        <v>24</v>
-      </c>
       <c t="s" r="I293" s="7">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>92</v>
+        <v>54</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10444,7 +10448,7 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>1505</v>
+        <v>637</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
@@ -10457,65 +10461,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>175</v>
+        <v>255</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c r="M294" s="7"/>
     </row>
     <row r="295" ht="15" customHeight="1">
-      <c t="s" r="A295" s="6">
-        <v>13</v>
-      </c>
-      <c r="B295" s="7">
-        <v>637</v>
-      </c>
-      <c t="s" r="C295" s="7">
-        <v>14</v>
-      </c>
+      <c r="A295" s="6"/>
+      <c r="B295" s="7"/>
+      <c r="C295" s="7"/>
       <c r="D295" s="7"/>
-      <c t="s" r="E295" s="7">
-        <v>324</v>
-      </c>
-      <c r="F295" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G295" s="8">
-        <v>153</v>
-      </c>
-      <c t="s" r="H295" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I295" s="7">
-        <v>254</v>
-      </c>
-      <c t="s" r="J295" s="7">
-        <v>29</v>
-      </c>
+      <c r="E295" s="7"/>
+      <c r="F295" s="7"/>
+      <c r="G295" s="8"/>
+      <c r="H295" s="8"/>
+      <c r="I295" s="7"/>
+      <c r="J295" s="7"/>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="6"/>
-      <c r="B296" s="7"/>
-      <c r="C296" s="7"/>
+      <c t="s" r="A296" s="6">
+        <v>13</v>
+      </c>
+      <c r="B296" s="7">
+        <v>1372</v>
+      </c>
+      <c t="s" r="C296" s="7">
+        <v>14</v>
+      </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="7"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="7"/>
-      <c r="J296" s="7"/>
+      <c t="s" r="E296" s="7">
+        <v>326</v>
+      </c>
+      <c r="F296" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G296" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H296" s="8">
+        <v>327</v>
+      </c>
+      <c t="s" r="I296" s="7">
+        <v>328</v>
+      </c>
+      <c t="s" r="J296" s="7">
+        <v>329</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
@@ -10525,7 +10529,7 @@
         <v>13</v>
       </c>
       <c r="B297" s="7">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C297" s="7">
         <v>14</v>
@@ -10538,16 +10542,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>327</v>
+        <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>329</v>
+        <v>235</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10558,7 +10562,7 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>1373</v>
+        <v>372</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
@@ -10571,16 +10575,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H298" s="8">
         <v>327</v>
       </c>
-      <c t="s" r="H298" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I298" s="7">
-        <v>273</v>
+        <v>78</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>235</v>
+        <v>149</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10591,7 +10595,7 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
@@ -10604,16 +10608,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>327</v>
+        <v>16</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10624,7 +10628,7 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>373</v>
+        <v>278</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
@@ -10637,16 +10641,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>327</v>
+        <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>68</v>
+        <v>318</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>174</v>
+        <v>54</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10657,7 +10661,7 @@
         <v>13</v>
       </c>
       <c r="B301" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="C301" s="7">
         <v>14</v>
@@ -10670,16 +10674,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>316</v>
+        <v>61</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>54</v>
+        <v>214</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10690,7 +10694,7 @@
         <v>13</v>
       </c>
       <c r="B302" s="7">
-        <v>279</v>
+        <v>1312</v>
       </c>
       <c t="s" r="C302" s="7">
         <v>14</v>
@@ -10703,16 +10707,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>61</v>
+        <v>200</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10723,7 +10727,7 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
@@ -10736,65 +10740,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>299</v>
+        <v>16</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>195</v>
+        <v>330</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>170</v>
+        <v>331</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c r="M303" s="7"/>
     </row>
     <row r="304" ht="14.25" customHeight="1">
-      <c t="s" r="A304" s="6">
-        <v>13</v>
-      </c>
-      <c r="B304" s="7">
-        <v>1311</v>
-      </c>
-      <c t="s" r="C304" s="7">
-        <v>14</v>
-      </c>
+      <c r="A304" s="6"/>
+      <c r="B304" s="7"/>
+      <c r="C304" s="7"/>
       <c r="D304" s="7"/>
-      <c t="s" r="E304" s="7">
-        <v>326</v>
-      </c>
-      <c r="F304" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G304" s="8">
-        <v>299</v>
-      </c>
-      <c t="s" r="H304" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I304" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="J304" s="7">
-        <v>331</v>
-      </c>
+      <c r="E304" s="7"/>
+      <c r="F304" s="7"/>
+      <c r="G304" s="8"/>
+      <c r="H304" s="8"/>
+      <c r="I304" s="7"/>
+      <c r="J304" s="7"/>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c r="M304" s="7"/>
     </row>
     <row r="305" ht="15" customHeight="1">
-      <c r="A305" s="6"/>
-      <c r="B305" s="7"/>
-      <c r="C305" s="7"/>
+      <c t="s" r="A305" s="6">
+        <v>13</v>
+      </c>
+      <c r="B305" s="7">
+        <v>125</v>
+      </c>
+      <c t="s" r="C305" s="7">
+        <v>14</v>
+      </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="7"/>
-      <c r="G305" s="8"/>
-      <c r="H305" s="8"/>
-      <c r="I305" s="7"/>
-      <c r="J305" s="7"/>
+      <c t="s" r="E305" s="7">
+        <v>332</v>
+      </c>
+      <c r="F305" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G305" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H305" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I305" s="7">
+        <v>181</v>
+      </c>
+      <c t="s" r="J305" s="7">
+        <v>333</v>
+      </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c r="M305" s="7"/>
@@ -10804,7 +10808,7 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>125</v>
+        <v>306</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
@@ -10817,16 +10821,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>180</v>
+        <v>226</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10837,7 +10841,7 @@
         <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
@@ -10850,65 +10854,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>299</v>
+        <v>16</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>226</v>
+        <v>280</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c r="M307" s="7"/>
     </row>
     <row r="308" ht="14.25" customHeight="1">
-      <c t="s" r="A308" s="6">
-        <v>13</v>
-      </c>
-      <c r="B308" s="7">
-        <v>305</v>
-      </c>
-      <c t="s" r="C308" s="7">
-        <v>14</v>
-      </c>
+      <c r="A308" s="6"/>
+      <c r="B308" s="7"/>
+      <c r="C308" s="7"/>
       <c r="D308" s="7"/>
-      <c t="s" r="E308" s="7">
-        <v>332</v>
-      </c>
-      <c r="F308" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G308" s="8">
-        <v>299</v>
-      </c>
-      <c t="s" r="H308" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I308" s="7">
-        <v>279</v>
-      </c>
-      <c t="s" r="J308" s="7">
-        <v>21</v>
-      </c>
+      <c r="E308" s="7"/>
+      <c r="F308" s="7"/>
+      <c r="G308" s="8"/>
+      <c r="H308" s="8"/>
+      <c r="I308" s="7"/>
+      <c r="J308" s="7"/>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c r="M308" s="7"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c r="A309" s="6"/>
-      <c r="B309" s="7"/>
-      <c r="C309" s="7"/>
+      <c t="s" r="A309" s="6">
+        <v>13</v>
+      </c>
+      <c r="B309" s="7">
+        <v>126</v>
+      </c>
+      <c t="s" r="C309" s="7">
+        <v>14</v>
+      </c>
       <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
-      <c r="F309" s="7"/>
-      <c r="G309" s="8"/>
-      <c r="H309" s="8"/>
-      <c r="I309" s="7"/>
-      <c r="J309" s="7"/>
+      <c t="s" r="E309" s="7">
+        <v>334</v>
+      </c>
+      <c r="F309" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G309" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H309" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I309" s="7">
+        <v>101</v>
+      </c>
+      <c t="s" r="J309" s="7">
+        <v>75</v>
+      </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c r="M309" s="7"/>
@@ -10918,7 +10922,7 @@
         <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
@@ -10931,16 +10935,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>101</v>
+        <v>206</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10951,7 +10955,7 @@
         <v>13</v>
       </c>
       <c r="B311" s="7">
-        <v>131</v>
+        <v>252</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
@@ -10964,16 +10968,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>206</v>
+        <v>268</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>79</v>
+        <v>139</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10984,7 +10988,7 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
@@ -10997,16 +11001,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>16</v>
+        <v>192</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11017,7 +11021,7 @@
         <v>13</v>
       </c>
       <c r="B313" s="7">
-        <v>253</v>
+        <v>3900</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
@@ -11030,16 +11034,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>191</v>
+        <v>16</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>253</v>
+        <v>200</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11047,10 +11051,10 @@
     </row>
     <row r="314" ht="14.25" customHeight="1">
       <c t="s" r="A314" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B314" s="7">
-        <v>3900</v>
+        <v>3901</v>
       </c>
       <c t="s" r="C314" s="7">
         <v>14</v>
@@ -11063,65 +11067,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>16</v>
+        <v>335</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>335</v>
+        <v>16</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>195</v>
+        <v>336</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>234</v>
+        <v>337</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c t="s" r="A315" s="6">
-        <v>32</v>
-      </c>
-      <c r="B315" s="7">
-        <v>3901</v>
-      </c>
-      <c t="s" r="C315" s="7">
-        <v>14</v>
-      </c>
+      <c r="A315" s="6"/>
+      <c r="B315" s="7"/>
+      <c r="C315" s="7"/>
       <c r="D315" s="7"/>
-      <c t="s" r="E315" s="7">
-        <v>334</v>
-      </c>
-      <c r="F315" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G315" s="8">
-        <v>335</v>
-      </c>
-      <c t="s" r="H315" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I315" s="7">
-        <v>336</v>
-      </c>
-      <c t="s" r="J315" s="7">
-        <v>337</v>
-      </c>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
+      <c r="G315" s="8"/>
+      <c r="H315" s="8"/>
+      <c r="I315" s="7"/>
+      <c r="J315" s="7"/>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
     </row>
     <row r="316" ht="14.25" customHeight="1">
-      <c r="A316" s="6"/>
-      <c r="B316" s="7"/>
-      <c r="C316" s="7"/>
+      <c t="s" r="A316" s="6">
+        <v>13</v>
+      </c>
+      <c r="B316" s="7">
+        <v>801</v>
+      </c>
+      <c t="s" r="C316" s="7">
+        <v>14</v>
+      </c>
       <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-      <c r="F316" s="7"/>
-      <c r="G316" s="8"/>
-      <c r="H316" s="8"/>
-      <c r="I316" s="7"/>
-      <c r="J316" s="7"/>
+      <c t="s" r="E316" s="7">
+        <v>338</v>
+      </c>
+      <c r="F316" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G316" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H316" s="8">
+        <v>266</v>
+      </c>
+      <c t="s" r="I316" s="7">
+        <v>41</v>
+      </c>
+      <c t="s" r="J316" s="7">
+        <v>339</v>
+      </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c r="M316" s="7"/>
@@ -11131,7 +11135,7 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
@@ -11144,16 +11148,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G317" s="8">
-        <v>16</v>
+        <v>266</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>265</v>
+        <v>16</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>41</v>
+        <v>340</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>339</v>
+        <v>91</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11164,7 +11168,7 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>802</v>
+        <v>362</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
@@ -11177,16 +11181,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>265</v>
+        <v>16</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>340</v>
+        <v>176</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11197,7 +11201,7 @@
         <v>13</v>
       </c>
       <c r="B319" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="C319" s="7">
         <v>14</v>
@@ -11210,16 +11214,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11230,7 +11234,7 @@
         <v>13</v>
       </c>
       <c r="B320" s="7">
-        <v>363</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
@@ -11243,16 +11247,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>111</v>
+        <v>16</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>291</v>
+        <v>55</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11260,10 +11264,10 @@
     </row>
     <row r="321" ht="14.25" customHeight="1">
       <c t="s" r="A321" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B321" s="7">
-        <v>3948</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
@@ -11276,65 +11280,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>16</v>
+        <v>341</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>341</v>
+        <v>16</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>55</v>
+        <v>342</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c r="M321" s="7"/>
     </row>
     <row r="322" ht="14.25" customHeight="1">
-      <c t="s" r="A322" s="6">
-        <v>32</v>
-      </c>
-      <c r="B322" s="7">
-        <v>3949</v>
-      </c>
-      <c t="s" r="C322" s="7">
-        <v>14</v>
-      </c>
+      <c r="A322" s="6"/>
+      <c r="B322" s="7"/>
+      <c r="C322" s="7"/>
       <c r="D322" s="7"/>
-      <c t="s" r="E322" s="7">
-        <v>338</v>
-      </c>
-      <c r="F322" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G322" s="8">
-        <v>341</v>
-      </c>
-      <c t="s" r="H322" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I322" s="7">
-        <v>342</v>
-      </c>
-      <c t="s" r="J322" s="7">
-        <v>126</v>
-      </c>
+      <c r="E322" s="7"/>
+      <c r="F322" s="7"/>
+      <c r="G322" s="8"/>
+      <c r="H322" s="8"/>
+      <c r="I322" s="7"/>
+      <c r="J322" s="7"/>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c r="M322" s="7"/>
     </row>
     <row r="323" ht="14.25" customHeight="1">
-      <c r="A323" s="6"/>
-      <c r="B323" s="7"/>
-      <c r="C323" s="7"/>
+      <c t="s" r="A323" s="6">
+        <v>13</v>
+      </c>
+      <c r="B323" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="C323" s="7">
+        <v>14</v>
+      </c>
       <c r="D323" s="7"/>
-      <c r="E323" s="7"/>
-      <c r="F323" s="7"/>
-      <c r="G323" s="8"/>
-      <c r="H323" s="8"/>
-      <c r="I323" s="7"/>
-      <c r="J323" s="7"/>
+      <c t="s" r="E323" s="7">
+        <v>343</v>
+      </c>
+      <c r="F323" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G323" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H323" s="8">
+        <v>38</v>
+      </c>
+      <c t="s" r="I323" s="7">
+        <v>18</v>
+      </c>
+      <c t="s" r="J323" s="7">
+        <v>159</v>
+      </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c r="M323" s="7"/>
@@ -11344,7 +11348,7 @@
         <v>13</v>
       </c>
       <c r="B324" s="7">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c t="s" r="C324" s="7">
         <v>14</v>
@@ -11357,16 +11361,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>18</v>
+        <v>226</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>159</v>
+        <v>340</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11377,7 +11381,7 @@
         <v>13</v>
       </c>
       <c r="B325" s="7">
-        <v>330</v>
+        <v>136</v>
       </c>
       <c t="s" r="C325" s="7">
         <v>14</v>
@@ -11390,16 +11394,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>226</v>
+        <v>174</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>340</v>
+        <v>228</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11410,7 +11414,7 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
@@ -11423,16 +11427,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>173</v>
+        <v>269</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>228</v>
+        <v>184</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11443,7 +11447,7 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>145</v>
+        <v>1875</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
@@ -11456,16 +11460,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>16</v>
+        <v>344</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>268</v>
+        <v>93</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>183</v>
+        <v>345</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11476,7 +11480,7 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
@@ -11489,65 +11493,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>16</v>
+        <v>344</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>344</v>
+        <v>16</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>93</v>
+        <v>346</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>345</v>
+        <v>283</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c r="M328" s="7"/>
     </row>
     <row r="329" ht="14.25" customHeight="1">
-      <c t="s" r="A329" s="6">
-        <v>13</v>
-      </c>
-      <c r="B329" s="7">
-        <v>1876</v>
-      </c>
-      <c t="s" r="C329" s="7">
-        <v>14</v>
-      </c>
+      <c r="A329" s="6"/>
+      <c r="B329" s="7"/>
+      <c r="C329" s="7"/>
       <c r="D329" s="7"/>
-      <c t="s" r="E329" s="7">
-        <v>343</v>
-      </c>
-      <c r="F329" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G329" s="8">
-        <v>344</v>
-      </c>
-      <c t="s" r="H329" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I329" s="7">
-        <v>346</v>
-      </c>
-      <c t="s" r="J329" s="7">
-        <v>282</v>
-      </c>
+      <c r="E329" s="7"/>
+      <c r="F329" s="7"/>
+      <c r="G329" s="8"/>
+      <c r="H329" s="8"/>
+      <c r="I329" s="7"/>
+      <c r="J329" s="7"/>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c r="M329" s="7"/>
     </row>
     <row r="330" ht="15" customHeight="1">
-      <c r="A330" s="6"/>
-      <c r="B330" s="7"/>
-      <c r="C330" s="7"/>
+      <c t="s" r="A330" s="6">
+        <v>13</v>
+      </c>
+      <c r="B330" s="7">
+        <v>811</v>
+      </c>
+      <c t="s" r="C330" s="7">
+        <v>14</v>
+      </c>
       <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
-      <c r="F330" s="7"/>
-      <c r="G330" s="8"/>
-      <c r="H330" s="8"/>
-      <c r="I330" s="7"/>
-      <c r="J330" s="7"/>
+      <c t="s" r="E330" s="7">
+        <v>347</v>
+      </c>
+      <c r="F330" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G330" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H330" s="8">
+        <v>257</v>
+      </c>
+      <c t="s" r="I330" s="7">
+        <v>170</v>
+      </c>
+      <c t="s" r="J330" s="7">
+        <v>325</v>
+      </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c r="M330" s="7"/>
@@ -11557,7 +11561,7 @@
         <v>13</v>
       </c>
       <c r="B331" s="7">
-        <v>811</v>
+        <v>984</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
@@ -11570,16 +11574,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>16</v>
+        <v>257</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>256</v>
+        <v>38</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>205</v>
+        <v>26</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11590,7 +11594,7 @@
         <v>13</v>
       </c>
       <c r="B332" s="7">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c t="s" r="C332" s="7">
         <v>14</v>
@@ -11603,16 +11607,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>256</v>
+        <v>38</v>
       </c>
       <c t="s" r="H332" s="8">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>26</v>
+        <v>300</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>348</v>
+        <v>217</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11623,7 +11627,7 @@
         <v>13</v>
       </c>
       <c r="B333" s="7">
-        <v>983</v>
+        <v>812</v>
       </c>
       <c t="s" r="C333" s="7">
         <v>14</v>
@@ -11636,65 +11640,65 @@
         <v>321</v>
       </c>
       <c t="s" r="G333" s="8">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>256</v>
+        <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>298</v>
+        <v>199</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>217</v>
+        <v>203</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c r="M333" s="7"/>
     </row>
     <row r="334" ht="14.25" customHeight="1">
-      <c t="s" r="A334" s="6">
-        <v>13</v>
-      </c>
-      <c r="B334" s="7">
-        <v>812</v>
-      </c>
-      <c t="s" r="C334" s="7">
-        <v>14</v>
-      </c>
+      <c r="A334" s="6"/>
+      <c r="B334" s="7"/>
+      <c r="C334" s="7"/>
       <c r="D334" s="7"/>
-      <c t="s" r="E334" s="7">
-        <v>347</v>
-      </c>
-      <c r="F334" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G334" s="8">
-        <v>256</v>
-      </c>
-      <c t="s" r="H334" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I334" s="7">
-        <v>199</v>
-      </c>
-      <c t="s" r="J334" s="7">
-        <v>202</v>
-      </c>
+      <c r="E334" s="7"/>
+      <c r="F334" s="7"/>
+      <c r="G334" s="8"/>
+      <c r="H334" s="8"/>
+      <c r="I334" s="7"/>
+      <c r="J334" s="7"/>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c r="M334" s="7"/>
     </row>
     <row r="335" ht="15" customHeight="1">
-      <c r="A335" s="6"/>
-      <c r="B335" s="7"/>
-      <c r="C335" s="7"/>
+      <c t="s" r="A335" s="6">
+        <v>13</v>
+      </c>
+      <c r="B335" s="7">
+        <v>952</v>
+      </c>
+      <c t="s" r="C335" s="7">
+        <v>14</v>
+      </c>
       <c r="D335" s="7"/>
-      <c r="E335" s="7"/>
-      <c r="F335" s="7"/>
-      <c r="G335" s="8"/>
-      <c r="H335" s="8"/>
-      <c r="I335" s="7"/>
-      <c r="J335" s="7"/>
+      <c t="s" r="E335" s="7">
+        <v>349</v>
+      </c>
+      <c r="F335" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G335" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H335" s="8">
+        <v>350</v>
+      </c>
+      <c t="s" r="I335" s="7">
+        <v>167</v>
+      </c>
+      <c t="s" r="J335" s="7">
+        <v>175</v>
+      </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c r="M335" s="7"/>
@@ -11704,7 +11708,7 @@
         <v>13</v>
       </c>
       <c r="B336" s="7">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c t="s" r="C336" s="7">
         <v>14</v>
@@ -11717,16 +11721,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
+        <v>350</v>
+      </c>
+      <c t="s" r="H336" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H336" s="8">
-        <v>350</v>
-      </c>
       <c t="s" r="I336" s="7">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>174</v>
+        <v>254</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11737,7 +11741,7 @@
         <v>13</v>
       </c>
       <c r="B337" s="7">
-        <v>953</v>
+        <v>465</v>
       </c>
       <c t="s" r="C337" s="7">
         <v>14</v>
@@ -11750,16 +11754,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G337" s="8">
-        <v>350</v>
+        <v>24</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>253</v>
+        <v>186</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
@@ -11770,7 +11774,7 @@
         <v>13</v>
       </c>
       <c r="B338" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c t="s" r="C338" s="7">
         <v>14</v>
@@ -11783,65 +11787,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="H338" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H338" s="8">
-        <v>162</v>
-      </c>
       <c t="s" r="I338" s="7">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>185</v>
+        <v>345</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c r="M338" s="7"/>
     </row>
     <row r="339" ht="14.25" customHeight="1">
-      <c t="s" r="A339" s="6">
-        <v>13</v>
-      </c>
-      <c r="B339" s="7">
-        <v>466</v>
-      </c>
-      <c t="s" r="C339" s="7">
-        <v>14</v>
-      </c>
+      <c r="A339" s="6"/>
+      <c r="B339" s="7"/>
+      <c r="C339" s="7"/>
       <c r="D339" s="7"/>
-      <c t="s" r="E339" s="7">
-        <v>349</v>
-      </c>
-      <c r="F339" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G339" s="8">
-        <v>162</v>
-      </c>
-      <c t="s" r="H339" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I339" s="7">
-        <v>114</v>
-      </c>
-      <c t="s" r="J339" s="7">
-        <v>345</v>
-      </c>
+      <c r="E339" s="7"/>
+      <c r="F339" s="7"/>
+      <c r="G339" s="8"/>
+      <c r="H339" s="8"/>
+      <c r="I339" s="7"/>
+      <c r="J339" s="7"/>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
       <c r="M339" s="7"/>
     </row>
     <row r="340" ht="15" customHeight="1">
-      <c r="A340" s="6"/>
-      <c r="B340" s="7"/>
-      <c r="C340" s="7"/>
+      <c t="s" r="A340" s="6">
+        <v>13</v>
+      </c>
+      <c r="B340" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="C340" s="7">
+        <v>351</v>
+      </c>
       <c r="D340" s="7"/>
-      <c r="E340" s="7"/>
-      <c r="F340" s="7"/>
-      <c r="G340" s="8"/>
-      <c r="H340" s="8"/>
-      <c r="I340" s="7"/>
-      <c r="J340" s="7"/>
+      <c t="s" r="E340" s="7">
+        <v>352</v>
+      </c>
+      <c r="F340" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G340" s="8">
+        <v>37</v>
+      </c>
+      <c t="s" r="H340" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I340" s="7">
+        <v>292</v>
+      </c>
+      <c t="s" r="J340" s="7">
+        <v>81</v>
+      </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c r="M340" s="7"/>
@@ -11851,10 +11855,10 @@
         <v>13</v>
       </c>
       <c r="B341" s="7">
-        <v>39</v>
+        <v>467</v>
       </c>
       <c t="s" r="C341" s="7">
-        <v>351</v>
+        <v>14</v>
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
@@ -11864,16 +11868,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>290</v>
+        <v>253</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>81</v>
+        <v>353</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -11884,7 +11888,7 @@
         <v>13</v>
       </c>
       <c r="B342" s="7">
-        <v>913</v>
+        <v>468</v>
       </c>
       <c t="s" r="C342" s="7">
         <v>14</v>
@@ -11897,16 +11901,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G342" s="8">
+        <v>162</v>
+      </c>
+      <c t="s" r="H342" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H342" s="8">
-        <v>353</v>
-      </c>
       <c t="s" r="I342" s="7">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11917,7 +11921,7 @@
         <v>13</v>
       </c>
       <c r="B343" s="7">
-        <v>914</v>
+        <v>161</v>
       </c>
       <c t="s" r="C343" s="7">
         <v>14</v>
@@ -11930,13 +11934,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>353</v>
+        <v>24</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>176</v>
+        <v>218</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>354</v>
@@ -11984,7 +11988,7 @@
         <v>145</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>67</v>
@@ -12017,10 +12021,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12053,7 +12057,7 @@
         <v>226</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12113,10 +12117,10 @@
         <v>24</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>140</v>
@@ -12143,7 +12147,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>24</v>
@@ -12178,7 +12182,7 @@
         <v>13</v>
       </c>
       <c r="B352" s="7">
-        <v>1981</v>
+        <v>421</v>
       </c>
       <c t="s" r="C352" s="7">
         <v>14</v>
@@ -12191,16 +12195,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G352" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H352" s="8">
         <v>358</v>
       </c>
-      <c t="s" r="H352" s="8">
-        <v>24</v>
-      </c>
       <c t="s" r="I352" s="7">
-        <v>226</v>
+        <v>274</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12211,7 +12215,7 @@
         <v>13</v>
       </c>
       <c r="B353" s="7">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c t="s" r="C353" s="7">
         <v>14</v>
@@ -12224,16 +12228,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
+        <v>358</v>
+      </c>
+      <c t="s" r="H353" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H353" s="8">
-        <v>359</v>
-      </c>
       <c t="s" r="I353" s="7">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>254</v>
+        <v>129</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12244,7 +12248,7 @@
         <v>13</v>
       </c>
       <c r="B354" s="7">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c t="s" r="C354" s="7">
         <v>14</v>
@@ -12257,16 +12261,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H354" s="8">
+        <v>38</v>
+      </c>
+      <c t="s" r="I354" s="7">
         <v>359</v>
       </c>
-      <c t="s" r="H354" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I354" s="7">
-        <v>194</v>
-      </c>
       <c t="s" r="J354" s="7">
-        <v>141</v>
+        <v>318</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12277,7 +12281,7 @@
         <v>13</v>
       </c>
       <c r="B355" s="7">
-        <v>7712</v>
+        <v>454</v>
       </c>
       <c t="s" r="C355" s="7">
         <v>14</v>
@@ -12290,16 +12294,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
+        <v>38</v>
+      </c>
+      <c t="s" r="H355" s="8">
         <v>24</v>
       </c>
-      <c t="s" r="H355" s="8">
-        <v>341</v>
-      </c>
       <c t="s" r="I355" s="7">
-        <v>73</v>
+        <v>176</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>360</v>
+        <v>323</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12307,10 +12311,10 @@
     </row>
     <row r="356" ht="14.25" customHeight="1">
       <c t="s" r="A356" s="6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B356" s="7">
-        <v>7713</v>
+        <v>495</v>
       </c>
       <c t="s" r="C356" s="7">
         <v>14</v>
@@ -12323,65 +12327,65 @@
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>341</v>
+        <v>24</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
       <c r="M356" s="7"/>
     </row>
     <row r="357" ht="14.25" customHeight="1">
-      <c r="A357" s="6"/>
-      <c r="B357" s="7"/>
-      <c r="C357" s="7"/>
+      <c t="s" r="A357" s="6">
+        <v>13</v>
+      </c>
+      <c r="B357" s="7">
+        <v>496</v>
+      </c>
+      <c t="s" r="C357" s="7">
+        <v>14</v>
+      </c>
       <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
-      <c r="F357" s="7"/>
-      <c r="G357" s="8"/>
-      <c r="H357" s="8"/>
-      <c r="I357" s="7"/>
-      <c r="J357" s="7"/>
+      <c t="s" r="E357" s="7">
+        <v>357</v>
+      </c>
+      <c r="F357" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G357" s="8">
+        <v>145</v>
+      </c>
+      <c t="s" r="H357" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I357" s="7">
+        <v>187</v>
+      </c>
+      <c t="s" r="J357" s="7">
+        <v>188</v>
+      </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c r="M357" s="7"/>
     </row>
     <row r="358" ht="14.25" customHeight="1">
-      <c t="s" r="A358" s="6">
-        <v>13</v>
-      </c>
-      <c r="B358" s="7">
-        <v>1382</v>
-      </c>
-      <c t="s" r="C358" s="7">
-        <v>14</v>
-      </c>
+      <c r="A358" s="6"/>
+      <c r="B358" s="7"/>
+      <c r="C358" s="7"/>
       <c r="D358" s="7"/>
-      <c t="s" r="E358" s="7">
-        <v>362</v>
-      </c>
-      <c r="F358" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G358" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H358" s="8">
-        <v>294</v>
-      </c>
-      <c t="s" r="I358" s="7">
-        <v>212</v>
-      </c>
-      <c t="s" r="J358" s="7">
-        <v>224</v>
-      </c>
+      <c r="E358" s="7"/>
+      <c r="F358" s="7"/>
+      <c r="G358" s="8"/>
+      <c r="H358" s="8"/>
+      <c r="I358" s="7"/>
+      <c r="J358" s="7"/>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c r="M358" s="7"/>
@@ -12391,29 +12395,29 @@
         <v>13</v>
       </c>
       <c r="B359" s="7">
-        <v>1383</v>
+        <v>1382</v>
       </c>
       <c t="s" r="C359" s="7">
         <v>14</v>
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>363</v>
+        <v>224</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12424,29 +12428,29 @@
         <v>13</v>
       </c>
       <c r="B360" s="7">
-        <v>304</v>
+        <v>1383</v>
       </c>
       <c t="s" r="C360" s="7">
         <v>14</v>
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>299</v>
+        <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>18</v>
+        <v>158</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>135</v>
+        <v>361</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12457,29 +12461,29 @@
         <v>13</v>
       </c>
       <c r="B361" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="C361" s="7">
         <v>14</v>
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>299</v>
+        <v>16</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>237</v>
+        <v>18</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>70</v>
+        <v>135</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12490,29 +12494,29 @@
         <v>13</v>
       </c>
       <c r="B362" s="7">
-        <v>374</v>
+        <v>303</v>
       </c>
       <c t="s" r="C362" s="7">
         <v>14</v>
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>16</v>
+        <v>301</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>327</v>
+        <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>304</v>
+        <v>70</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12523,29 +12527,29 @@
         <v>13</v>
       </c>
       <c r="B363" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c t="s" r="C363" s="7">
         <v>14</v>
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H363" s="8">
         <v>327</v>
       </c>
-      <c t="s" r="H363" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I363" s="7">
-        <v>161</v>
+        <v>220</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>276</v>
+        <v>306</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12556,29 +12560,29 @@
         <v>13</v>
       </c>
       <c r="B364" s="7">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c t="s" r="C364" s="7">
         <v>14</v>
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F364" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>16</v>
+        <v>327</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>213</v>
+        <v>161</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>140</v>
+        <v>277</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12589,78 +12593,78 @@
         <v>13</v>
       </c>
       <c r="B365" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c t="s" r="C365" s="7">
         <v>14</v>
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F365" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>294</v>
+        <v>16</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>16</v>
+        <v>296</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>93</v>
+        <v>213</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>45</v>
+        <v>140</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c r="M365" s="7"/>
     </row>
     <row r="366" ht="14.25" customHeight="1">
-      <c r="A366" s="6"/>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
+      <c t="s" r="A366" s="6">
+        <v>13</v>
+      </c>
+      <c r="B366" s="7">
+        <v>385</v>
+      </c>
+      <c t="s" r="C366" s="7">
+        <v>14</v>
+      </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="8"/>
-      <c r="H366" s="8"/>
-      <c r="I366" s="7"/>
-      <c r="J366" s="7"/>
+      <c t="s" r="E366" s="7">
+        <v>360</v>
+      </c>
+      <c r="F366" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G366" s="8">
+        <v>296</v>
+      </c>
+      <c t="s" r="H366" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I366" s="7">
+        <v>93</v>
+      </c>
+      <c t="s" r="J366" s="7">
+        <v>45</v>
+      </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c r="M366" s="7"/>
     </row>
     <row r="367" ht="14.25" customHeight="1">
-      <c t="s" r="A367" s="6">
-        <v>13</v>
-      </c>
-      <c r="B367" s="7">
-        <v>628</v>
-      </c>
-      <c t="s" r="C367" s="7">
-        <v>14</v>
-      </c>
+      <c r="A367" s="6"/>
+      <c r="B367" s="7"/>
+      <c r="C367" s="7"/>
       <c r="D367" s="7"/>
-      <c t="s" r="E367" s="7">
-        <v>364</v>
-      </c>
-      <c r="F367" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G367" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H367" s="8">
-        <v>153</v>
-      </c>
-      <c t="s" r="I367" s="7">
-        <v>365</v>
-      </c>
-      <c t="s" r="J367" s="7">
-        <v>127</v>
-      </c>
+      <c r="E367" s="7"/>
+      <c r="F367" s="7"/>
+      <c r="G367" s="8"/>
+      <c r="H367" s="8"/>
+      <c r="I367" s="7"/>
+      <c r="J367" s="7"/>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c r="M367" s="7"/>
@@ -12670,29 +12674,29 @@
         <v>13</v>
       </c>
       <c r="B368" s="7">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c t="s" r="C368" s="7">
         <v>14</v>
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H368" s="8">
         <v>153</v>
       </c>
-      <c t="s" r="H368" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I368" s="7">
-        <v>251</v>
+        <v>363</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12703,29 +12707,29 @@
         <v>13</v>
       </c>
       <c r="B369" s="7">
-        <v>210</v>
+        <v>627</v>
       </c>
       <c t="s" r="C369" s="7">
         <v>14</v>
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>143</v>
+        <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>293</v>
+        <v>251</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>42</v>
+        <v>135</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12736,29 +12740,29 @@
         <v>13</v>
       </c>
       <c r="B370" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="C370" s="7">
         <v>14</v>
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H370" s="8">
         <v>143</v>
       </c>
-      <c t="s" r="H370" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I370" s="7">
-        <v>348</v>
+        <v>295</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>366</v>
+        <v>42</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12769,29 +12773,29 @@
         <v>13</v>
       </c>
       <c r="B371" s="7">
-        <v>394</v>
+        <v>211</v>
       </c>
       <c t="s" r="C371" s="7">
         <v>14</v>
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
+        <v>362</v>
+      </c>
+      <c r="F371" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G371" s="8">
+        <v>143</v>
+      </c>
+      <c t="s" r="H371" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I371" s="7">
+        <v>348</v>
+      </c>
+      <c t="s" r="J371" s="7">
         <v>364</v>
-      </c>
-      <c r="F371" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G371" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H371" s="8">
-        <v>359</v>
-      </c>
-      <c t="s" r="I371" s="7">
-        <v>254</v>
-      </c>
-      <c t="s" r="J371" s="7">
-        <v>165</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12802,29 +12806,29 @@
         <v>13</v>
       </c>
       <c r="B372" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c t="s" r="C372" s="7">
         <v>14</v>
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>359</v>
+        <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>16</v>
+        <v>358</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>44</v>
+        <v>255</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12835,29 +12839,29 @@
         <v>13</v>
       </c>
       <c r="B373" s="7">
-        <v>648</v>
+        <v>395</v>
       </c>
       <c t="s" r="C373" s="7">
         <v>14</v>
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>16</v>
+        <v>358</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>195</v>
+        <v>44</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>300</v>
+        <v>199</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12868,78 +12872,78 @@
         <v>13</v>
       </c>
       <c r="B374" s="7">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c t="s" r="C374" s="7">
         <v>14</v>
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H374" s="8">
         <v>153</v>
       </c>
-      <c t="s" r="H374" s="8">
-        <v>16</v>
-      </c>
       <c t="s" r="I374" s="7">
-        <v>345</v>
+        <v>200</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>209</v>
+        <v>302</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c r="M374" s="7"/>
     </row>
     <row r="375" ht="15" customHeight="1">
-      <c r="A375" s="6"/>
-      <c r="B375" s="7"/>
-      <c r="C375" s="7"/>
+      <c t="s" r="A375" s="6">
+        <v>13</v>
+      </c>
+      <c r="B375" s="7">
+        <v>647</v>
+      </c>
+      <c t="s" r="C375" s="7">
+        <v>14</v>
+      </c>
       <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" s="7"/>
-      <c r="G375" s="8"/>
-      <c r="H375" s="8"/>
-      <c r="I375" s="7"/>
-      <c r="J375" s="7"/>
+      <c t="s" r="E375" s="7">
+        <v>362</v>
+      </c>
+      <c r="F375" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G375" s="8">
+        <v>153</v>
+      </c>
+      <c t="s" r="H375" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I375" s="7">
+        <v>345</v>
+      </c>
+      <c t="s" r="J375" s="7">
+        <v>209</v>
+      </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c r="M375" s="7"/>
     </row>
     <row r="376" ht="14.25" customHeight="1">
-      <c t="s" r="A376" s="6">
-        <v>13</v>
-      </c>
-      <c r="B376" s="7">
-        <v>431</v>
-      </c>
-      <c t="s" r="C376" s="7">
-        <v>14</v>
-      </c>
+      <c r="A376" s="6"/>
+      <c r="B376" s="7"/>
+      <c r="C376" s="7"/>
       <c r="D376" s="7"/>
-      <c t="s" r="E376" s="7">
-        <v>367</v>
-      </c>
-      <c r="F376" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G376" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H376" s="8">
-        <v>294</v>
-      </c>
-      <c t="s" r="I376" s="7">
-        <v>296</v>
-      </c>
-      <c t="s" r="J376" s="7">
-        <v>264</v>
-      </c>
+      <c r="E376" s="7"/>
+      <c r="F376" s="7"/>
+      <c r="G376" s="8"/>
+      <c r="H376" s="8"/>
+      <c r="I376" s="7"/>
+      <c r="J376" s="7"/>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c r="M376" s="7"/>
@@ -12949,29 +12953,29 @@
         <v>13</v>
       </c>
       <c r="B377" s="7">
-        <v>430</v>
+        <v>1981</v>
       </c>
       <c t="s" r="C377" s="7">
         <v>14</v>
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>294</v>
+        <v>366</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>134</v>
+        <v>226</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -12982,14 +12986,14 @@
         <v>13</v>
       </c>
       <c r="B378" s="7">
-        <v>463</v>
+        <v>423</v>
       </c>
       <c t="s" r="C378" s="7">
         <v>14</v>
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -12998,13 +13002,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H378" s="8">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>174</v>
+        <v>255</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13015,29 +13019,29 @@
         <v>13</v>
       </c>
       <c r="B379" s="7">
-        <v>464</v>
+        <v>424</v>
       </c>
       <c t="s" r="C379" s="7">
         <v>14</v>
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G379" s="8">
-        <v>162</v>
+        <v>358</v>
       </c>
       <c t="s" r="H379" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>91</v>
+        <v>353</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>233</v>
+        <v>141</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13048,14 +13052,14 @@
         <v>13</v>
       </c>
       <c r="B380" s="7">
-        <v>567</v>
+        <v>7712</v>
       </c>
       <c t="s" r="C380" s="7">
         <v>14</v>
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13064,13 +13068,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>194</v>
+        <v>367</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13078,66 +13082,48 @@
     </row>
     <row r="381" ht="14.25" customHeight="1">
       <c t="s" r="A381" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B381" s="7">
-        <v>568</v>
+        <v>7713</v>
       </c>
       <c t="s" r="C381" s="7">
         <v>14</v>
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>299</v>
+        <v>341</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I381" s="7">
+        <v>123</v>
+      </c>
+      <c t="s" r="J381" s="7">
         <v>368</v>
-      </c>
-      <c t="s" r="J381" s="7">
-        <v>56</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c r="M381" s="7"/>
     </row>
     <row r="382" ht="14.25" customHeight="1">
-      <c t="s" r="A382" s="6">
-        <v>13</v>
-      </c>
-      <c r="B382" s="7">
-        <v>1127</v>
-      </c>
-      <c t="s" r="C382" s="7">
-        <v>14</v>
-      </c>
+      <c r="A382" s="6"/>
+      <c r="B382" s="7"/>
+      <c r="C382" s="7"/>
       <c r="D382" s="7"/>
-      <c t="s" r="E382" s="7">
-        <v>367</v>
-      </c>
-      <c r="F382" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G382" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="H382" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I382" s="7">
-        <v>199</v>
-      </c>
-      <c t="s" r="J382" s="7">
-        <v>178</v>
-      </c>
+      <c r="E382" s="7"/>
+      <c r="F382" s="7"/>
+      <c r="G382" s="8"/>
+      <c r="H382" s="8"/>
+      <c r="I382" s="7"/>
+      <c r="J382" s="7"/>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c r="M382" s="7"/>
@@ -13147,45 +13133,63 @@
         <v>13</v>
       </c>
       <c r="B383" s="7">
-        <v>1128</v>
+        <v>981</v>
       </c>
       <c t="s" r="C383" s="7">
         <v>14</v>
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F383" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>96</v>
+        <v>134</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>369</v>
+        <v>149</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c r="M383" s="7"/>
     </row>
     <row r="384" ht="14.25" customHeight="1">
-      <c r="A384" s="6"/>
-      <c r="B384" s="7"/>
-      <c r="C384" s="7"/>
+      <c t="s" r="A384" s="6">
+        <v>13</v>
+      </c>
+      <c r="B384" s="7">
+        <v>133</v>
+      </c>
+      <c t="s" r="C384" s="7">
+        <v>14</v>
+      </c>
       <c r="D384" s="7"/>
-      <c r="E384" s="7"/>
-      <c r="F384" s="7"/>
-      <c r="G384" s="8"/>
-      <c r="H384" s="8"/>
-      <c r="I384" s="7"/>
-      <c r="J384" s="7"/>
+      <c t="s" r="E384" s="7">
+        <v>369</v>
+      </c>
+      <c r="F384" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G384" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="H384" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I384" s="7">
+        <v>52</v>
+      </c>
+      <c t="s" r="J384" s="7">
+        <v>21</v>
+      </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c r="M384" s="7"/>
@@ -13195,29 +13199,29 @@
         <v>13</v>
       </c>
       <c r="B385" s="7">
-        <v>981</v>
+        <v>140</v>
       </c>
       <c t="s" r="C385" s="7">
         <v>14</v>
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>134</v>
+        <v>207</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>149</v>
+        <v>255</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13228,14 +13232,14 @@
         <v>13</v>
       </c>
       <c r="B386" s="7">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c t="s" r="C386" s="7">
         <v>14</v>
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13247,10 +13251,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>52</v>
+        <v>353</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13261,14 +13265,14 @@
         <v>13</v>
       </c>
       <c r="B387" s="7">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c t="s" r="C387" s="7">
         <v>14</v>
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13280,10 +13284,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13291,17 +13295,17 @@
     </row>
     <row r="388" ht="14.25" customHeight="1">
       <c t="s" r="A388" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B388" s="7">
-        <v>151</v>
+        <v>982</v>
       </c>
       <c t="s" r="C388" s="7">
         <v>14</v>
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13310,57 +13314,39 @@
         <v>24</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>16</v>
+        <v>66</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>194</v>
+        <v>342</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>45</v>
+        <v>274</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c r="M388" s="7"/>
     </row>
     <row r="389" ht="14.25" customHeight="1">
-      <c t="s" r="A389" s="6">
-        <v>13</v>
-      </c>
-      <c r="B389" s="7">
-        <v>160</v>
-      </c>
-      <c t="s" r="C389" s="7">
-        <v>14</v>
-      </c>
+      <c r="A389" s="6"/>
+      <c r="B389" s="7"/>
+      <c r="C389" s="7"/>
       <c r="D389" s="7"/>
-      <c t="s" r="E389" s="7">
-        <v>370</v>
-      </c>
-      <c r="F389" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G389" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H389" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I389" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="J389" s="7">
-        <v>239</v>
-      </c>
+      <c r="E389" s="7"/>
+      <c r="F389" s="7"/>
+      <c r="G389" s="8"/>
+      <c r="H389" s="8"/>
+      <c r="I389" s="7"/>
+      <c r="J389" s="7"/>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c r="M389" s="7"/>
     </row>
     <row r="390" ht="15" customHeight="1">
       <c t="s" r="A390" s="6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B390" s="7">
-        <v>982</v>
+        <v>302</v>
       </c>
       <c t="s" r="C390" s="7">
         <v>14</v>
@@ -13370,35 +13356,53 @@
         <v>370</v>
       </c>
       <c r="F390" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>66</v>
+        <v>301</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>342</v>
+        <v>264</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c r="M390" s="7"/>
     </row>
     <row r="391" ht="14.25" customHeight="1">
-      <c r="A391" s="6"/>
-      <c r="B391" s="7"/>
-      <c r="C391" s="7"/>
+      <c t="s" r="A391" s="6">
+        <v>13</v>
+      </c>
+      <c r="B391" s="7">
+        <v>301</v>
+      </c>
+      <c t="s" r="C391" s="7">
+        <v>14</v>
+      </c>
       <c r="D391" s="7"/>
-      <c r="E391" s="7"/>
-      <c r="F391" s="7"/>
-      <c r="G391" s="8"/>
-      <c r="H391" s="8"/>
-      <c r="I391" s="7"/>
-      <c r="J391" s="7"/>
+      <c t="s" r="E391" s="7">
+        <v>370</v>
+      </c>
+      <c r="F391" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G391" s="8">
+        <v>301</v>
+      </c>
+      <c t="s" r="H391" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I391" s="7">
+        <v>371</v>
+      </c>
+      <c t="s" r="J391" s="7">
+        <v>18</v>
+      </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c r="M391" s="7"/>
@@ -13408,14 +13412,14 @@
         <v>13</v>
       </c>
       <c r="B392" s="7">
-        <v>302</v>
+        <v>274</v>
       </c>
       <c t="s" r="C392" s="7">
         <v>14</v>
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -13424,13 +13428,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>284</v>
+        <v>174</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13441,29 +13445,29 @@
         <v>13</v>
       </c>
       <c r="B393" s="7">
-        <v>301</v>
+        <v>275</v>
       </c>
       <c t="s" r="C393" s="7">
         <v>14</v>
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>299</v>
+        <v>137</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>372</v>
+        <v>175</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>18</v>
+        <v>207</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13474,14 +13478,14 @@
         <v>13</v>
       </c>
       <c r="B394" s="7">
-        <v>274</v>
+        <v>376</v>
       </c>
       <c t="s" r="C394" s="7">
         <v>14</v>
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -13490,13 +13494,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>137</v>
+        <v>327</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>286</v>
+        <v>139</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>173</v>
+        <v>82</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13507,29 +13511,29 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>275</v>
+        <v>377</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>137</v>
+        <v>327</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13540,14 +13544,14 @@
         <v>13</v>
       </c>
       <c r="B396" s="7">
-        <v>376</v>
+        <v>150</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13556,47 +13560,29 @@
         <v>16</v>
       </c>
       <c t="s" r="H396" s="8">
-        <v>327</v>
+        <v>24</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>82</v>
+        <v>239</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c r="M396" s="7"/>
     </row>
     <row r="397" ht="14.25" customHeight="1">
-      <c t="s" r="A397" s="6">
-        <v>13</v>
-      </c>
-      <c r="B397" s="7">
-        <v>377</v>
-      </c>
-      <c t="s" r="C397" s="7">
-        <v>14</v>
-      </c>
+      <c r="A397" s="6"/>
+      <c r="B397" s="7"/>
+      <c r="C397" s="7"/>
       <c r="D397" s="7"/>
-      <c t="s" r="E397" s="7">
-        <v>371</v>
-      </c>
-      <c r="F397" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G397" s="8">
-        <v>327</v>
-      </c>
-      <c t="s" r="H397" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I397" s="7">
-        <v>62</v>
-      </c>
-      <c t="s" r="J397" s="7">
-        <v>201</v>
-      </c>
+      <c r="E397" s="7"/>
+      <c r="F397" s="7"/>
+      <c r="G397" s="8"/>
+      <c r="H397" s="8"/>
+      <c r="I397" s="7"/>
+      <c r="J397" s="7"/>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c r="M397" s="7"/>
@@ -13606,45 +13592,63 @@
         <v>13</v>
       </c>
       <c r="B398" s="7">
-        <v>150</v>
+        <v>1771</v>
       </c>
       <c t="s" r="C398" s="7">
         <v>14</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G398" s="8">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>24</v>
+        <v>94</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c r="M398" s="7"/>
     </row>
     <row r="399" ht="14.25" customHeight="1">
-      <c r="A399" s="6"/>
-      <c r="B399" s="7"/>
-      <c r="C399" s="7"/>
+      <c t="s" r="A399" s="6">
+        <v>13</v>
+      </c>
+      <c r="B399" s="7">
+        <v>1772</v>
+      </c>
+      <c t="s" r="C399" s="7">
+        <v>14</v>
+      </c>
       <c r="D399" s="7"/>
-      <c r="E399" s="7"/>
-      <c r="F399" s="7"/>
-      <c r="G399" s="8"/>
-      <c r="H399" s="8"/>
-      <c r="I399" s="7"/>
-      <c r="J399" s="7"/>
+      <c t="s" r="E399" s="7">
+        <v>372</v>
+      </c>
+      <c r="F399" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G399" s="8">
+        <v>94</v>
+      </c>
+      <c t="s" r="H399" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I399" s="7">
+        <v>109</v>
+      </c>
+      <c t="s" r="J399" s="7">
+        <v>304</v>
+      </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c r="M399" s="7"/>
@@ -13654,14 +13658,14 @@
         <v>13</v>
       </c>
       <c r="B400" s="7">
-        <v>1771</v>
+        <v>1453</v>
       </c>
       <c t="s" r="C400" s="7">
         <v>14</v>
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13670,13 +13674,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>180</v>
+        <v>267</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>18</v>
+        <v>318</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13687,29 +13691,29 @@
         <v>13</v>
       </c>
       <c r="B401" s="7">
-        <v>1772</v>
+        <v>1454</v>
       </c>
       <c t="s" r="C401" s="7">
         <v>14</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>94</v>
+        <v>38</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>109</v>
+        <v>207</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>302</v>
+        <v>213</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13720,14 +13724,14 @@
         <v>13</v>
       </c>
       <c r="B402" s="7">
-        <v>1453</v>
+        <v>141</v>
       </c>
       <c t="s" r="C402" s="7">
         <v>14</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F402" s="7">
         <v>320</v>
@@ -13736,47 +13740,29 @@
         <v>24</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>266</v>
+        <v>373</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>316</v>
+        <v>187</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c r="M402" s="7"/>
     </row>
     <row r="403" ht="14.25" customHeight="1">
-      <c t="s" r="A403" s="6">
-        <v>13</v>
-      </c>
-      <c r="B403" s="7">
-        <v>1454</v>
-      </c>
-      <c t="s" r="C403" s="7">
-        <v>14</v>
-      </c>
+      <c r="A403" s="6"/>
+      <c r="B403" s="7"/>
+      <c r="C403" s="7"/>
       <c r="D403" s="7"/>
-      <c t="s" r="E403" s="7">
-        <v>373</v>
-      </c>
-      <c r="F403" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G403" s="8">
-        <v>38</v>
-      </c>
-      <c t="s" r="H403" s="8">
-        <v>24</v>
-      </c>
-      <c t="s" r="I403" s="7">
-        <v>207</v>
-      </c>
-      <c t="s" r="J403" s="7">
-        <v>213</v>
-      </c>
+      <c r="E403" s="7"/>
+      <c r="F403" s="7"/>
+      <c r="G403" s="8"/>
+      <c r="H403" s="8"/>
+      <c r="I403" s="7"/>
+      <c r="J403" s="7"/>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c r="M403" s="7"/>
@@ -13786,45 +13772,63 @@
         <v>13</v>
       </c>
       <c r="B404" s="7">
-        <v>141</v>
+        <v>719</v>
       </c>
       <c t="s" r="C404" s="7">
         <v>14</v>
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F404" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>24</v>
+        <v>153</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>374</v>
+        <v>158</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c r="M404" s="7"/>
     </row>
     <row r="405" ht="15" customHeight="1">
-      <c r="A405" s="6"/>
-      <c r="B405" s="7"/>
-      <c r="C405" s="7"/>
+      <c t="s" r="A405" s="6">
+        <v>13</v>
+      </c>
+      <c r="B405" s="7">
+        <v>718</v>
+      </c>
+      <c t="s" r="C405" s="7">
+        <v>14</v>
+      </c>
       <c r="D405" s="7"/>
-      <c r="E405" s="7"/>
-      <c r="F405" s="7"/>
-      <c r="G405" s="8"/>
-      <c r="H405" s="8"/>
-      <c r="I405" s="7"/>
-      <c r="J405" s="7"/>
+      <c t="s" r="E405" s="7">
+        <v>374</v>
+      </c>
+      <c r="F405" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G405" s="8">
+        <v>38</v>
+      </c>
+      <c t="s" r="H405" s="8">
+        <v>153</v>
+      </c>
+      <c t="s" r="I405" s="7">
+        <v>246</v>
+      </c>
+      <c t="s" r="J405" s="7">
+        <v>136</v>
+      </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c r="M405" s="7"/>
@@ -13834,14 +13838,14 @@
         <v>13</v>
       </c>
       <c r="B406" s="7">
-        <v>719</v>
+        <v>8890</v>
       </c>
       <c t="s" r="C406" s="7">
         <v>14</v>
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -13850,13 +13854,13 @@
         <v>153</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>38</v>
+        <v>281</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>205</v>
+        <v>103</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13867,29 +13871,29 @@
         <v>13</v>
       </c>
       <c r="B407" s="7">
-        <v>718</v>
+        <v>8891</v>
       </c>
       <c t="s" r="C407" s="7">
         <v>14</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>38</v>
+        <v>281</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>246</v>
+        <v>150</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>136</v>
+        <v>213</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13900,14 +13904,14 @@
         <v>13</v>
       </c>
       <c r="B408" s="7">
-        <v>8890</v>
+        <v>8892</v>
       </c>
       <c t="s" r="C408" s="7">
         <v>14</v>
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -13916,13 +13920,13 @@
         <v>153</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>192</v>
+        <v>93</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13933,29 +13937,29 @@
         <v>13</v>
       </c>
       <c r="B409" s="7">
-        <v>8891</v>
+        <v>8893</v>
       </c>
       <c t="s" r="C409" s="7">
         <v>14</v>
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>153</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>150</v>
+        <v>330</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13963,17 +13967,17 @@
     </row>
     <row r="410" ht="15" customHeight="1">
       <c t="s" r="A410" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="B410" s="7">
-        <v>8892</v>
+        <v>988</v>
       </c>
       <c t="s" r="C410" s="7">
         <v>14</v>
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13982,57 +13986,39 @@
         <v>153</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>280</v>
+        <v>66</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>354</v>
+        <v>329</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c r="M410" s="7"/>
     </row>
     <row r="411" ht="14.25" customHeight="1">
-      <c t="s" r="A411" s="6">
-        <v>13</v>
-      </c>
-      <c r="B411" s="7">
-        <v>8893</v>
-      </c>
-      <c t="s" r="C411" s="7">
-        <v>14</v>
-      </c>
+      <c r="A411" s="6"/>
+      <c r="B411" s="7"/>
+      <c r="C411" s="7"/>
       <c r="D411" s="7"/>
-      <c t="s" r="E411" s="7">
-        <v>375</v>
-      </c>
-      <c r="F411" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G411" s="8">
-        <v>280</v>
-      </c>
-      <c t="s" r="H411" s="8">
-        <v>153</v>
-      </c>
-      <c t="s" r="I411" s="7">
-        <v>330</v>
-      </c>
-      <c t="s" r="J411" s="7">
-        <v>239</v>
-      </c>
+      <c r="E411" s="7"/>
+      <c r="F411" s="7"/>
+      <c r="G411" s="8"/>
+      <c r="H411" s="8"/>
+      <c r="I411" s="7"/>
+      <c r="J411" s="7"/>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c r="M411" s="7"/>
     </row>
     <row r="412" ht="14.25" customHeight="1">
       <c t="s" r="A412" s="6">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="B412" s="7">
-        <v>988</v>
+        <v>431</v>
       </c>
       <c t="s" r="C412" s="7">
         <v>14</v>
@@ -14042,35 +14028,53 @@
         <v>375</v>
       </c>
       <c r="F412" s="7">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>153</v>
+        <v>24</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>66</v>
+        <v>296</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>64</v>
+        <v>298</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>329</v>
+        <v>265</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c r="M412" s="7"/>
     </row>
     <row r="413" ht="14.25" customHeight="1">
-      <c r="A413" s="6"/>
-      <c r="B413" s="7"/>
-      <c r="C413" s="7"/>
+      <c t="s" r="A413" s="6">
+        <v>13</v>
+      </c>
+      <c r="B413" s="7">
+        <v>430</v>
+      </c>
+      <c t="s" r="C413" s="7">
+        <v>14</v>
+      </c>
       <c r="D413" s="7"/>
-      <c r="E413" s="7"/>
-      <c r="F413" s="7"/>
-      <c r="G413" s="8"/>
-      <c r="H413" s="8"/>
-      <c r="I413" s="7"/>
-      <c r="J413" s="7"/>
+      <c t="s" r="E413" s="7">
+        <v>375</v>
+      </c>
+      <c r="F413" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G413" s="8">
+        <v>296</v>
+      </c>
+      <c t="s" r="H413" s="8">
+        <v>24</v>
+      </c>
+      <c t="s" r="I413" s="7">
+        <v>134</v>
+      </c>
+      <c t="s" r="J413" s="7">
+        <v>128</v>
+      </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c r="M413" s="7"/>
@@ -14080,14 +14084,14 @@
         <v>13</v>
       </c>
       <c r="B414" s="7">
-        <v>421</v>
+        <v>463</v>
       </c>
       <c t="s" r="C414" s="7">
         <v>14</v>
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14096,13 +14100,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>359</v>
+        <v>162</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>273</v>
+        <v>173</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>147</v>
+        <v>175</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14113,29 +14117,29 @@
         <v>13</v>
       </c>
       <c r="B415" s="7">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c t="s" r="C415" s="7">
         <v>14</v>
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>359</v>
+        <v>162</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>148</v>
+        <v>91</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>129</v>
+        <v>233</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14146,14 +14150,14 @@
         <v>13</v>
       </c>
       <c r="B416" s="7">
-        <v>451</v>
+        <v>567</v>
       </c>
       <c t="s" r="C416" s="7">
         <v>14</v>
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14162,13 +14166,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H416" s="8">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>377</v>
+        <v>54</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -14179,29 +14183,29 @@
         <v>13</v>
       </c>
       <c r="B417" s="7">
-        <v>454</v>
+        <v>568</v>
       </c>
       <c t="s" r="C417" s="7">
         <v>14</v>
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G417" s="8">
-        <v>38</v>
+        <v>301</v>
       </c>
       <c t="s" r="H417" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>175</v>
+        <v>376</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>321</v>
+        <v>56</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14212,14 +14216,14 @@
         <v>13</v>
       </c>
       <c r="B418" s="7">
-        <v>495</v>
+        <v>1127</v>
       </c>
       <c t="s" r="C418" s="7">
         <v>14</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -14228,13 +14232,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>62</v>
+        <v>199</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>287</v>
+        <v>179</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14245,29 +14249,29 @@
         <v>13</v>
       </c>
       <c r="B419" s="7">
-        <v>496</v>
+        <v>1128</v>
       </c>
       <c t="s" r="C419" s="7">
         <v>14</v>
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>186</v>
+        <v>96</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>187</v>
+        <v>377</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14312,7 +14316,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c t="s" r="J421" s="7">
         <v>134</v>
@@ -14348,7 +14352,7 @@
         <v>246</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14381,7 +14385,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14408,10 +14412,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H424" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>114</v>
@@ -14438,7 +14442,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G425" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H425" s="8">
         <v>16</v>
@@ -14624,10 +14628,10 @@
         <v>24</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14666,7 +14670,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G433" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H433" s="8">
         <v>24</v>
@@ -14675,7 +14679,7 @@
         <v>251</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -14741,7 +14745,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
@@ -14771,7 +14775,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I436" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c t="s" r="J436" s="7">
         <v>165</v>
@@ -14855,7 +14859,7 @@
         <v>126</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14888,7 +14892,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
@@ -14915,10 +14919,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>356</v>
@@ -14945,7 +14949,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>16</v>
@@ -14954,7 +14958,7 @@
         <v>21</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
@@ -14981,7 +14985,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>151</v>
@@ -15011,7 +15015,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>16</v>
@@ -15083,7 +15087,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>383</v>
@@ -15194,13 +15198,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="I450" s="7">
         <v>226</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
@@ -15224,13 +15228,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>24</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>81</v>
@@ -15440,13 +15444,13 @@
         <v>24</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15470,7 +15474,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>24</v>
@@ -15509,10 +15513,10 @@
         <v>391</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>288</v>
+        <v>354</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15545,7 +15549,7 @@
         <v>392</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15623,7 +15627,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I464" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J464" s="7">
         <v>70</v>
@@ -15656,10 +15660,10 @@
         <v>94</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15701,7 +15705,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H467" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I467" s="7">
         <v>127</v>
@@ -15731,7 +15735,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G468" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H468" s="8">
         <v>16</v>
@@ -15767,10 +15771,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H469" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>377</v>
+        <v>359</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>348</v>
@@ -15797,13 +15801,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G470" s="8">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c t="s" r="H470" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J470" s="7">
         <v>395</v>
@@ -15836,7 +15840,7 @@
         <v>24</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>194</v>
+        <v>353</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>45</v>
@@ -15920,7 +15924,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
@@ -16008,7 +16012,7 @@
       </c>
       <c r="L477" s="7"/>
       <c t="s" r="M477" s="7">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="478" ht="14.25" customHeight="1">
@@ -16041,7 +16045,7 @@
         <v>215</v>
       </c>
       <c t="s" r="K478" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
@@ -16075,7 +16079,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16204,7 +16208,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16267,7 +16271,7 @@
         <v>94</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>322</v>
+        <v>289</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>405</v>
@@ -16318,7 +16322,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -16348,7 +16352,7 @@
         <v>407</v>
       </c>
       <c t="s" r="I489" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J489" s="7">
         <v>56</v>
@@ -16432,7 +16436,7 @@
         <v>135</v>
       </c>
       <c t="s" r="J492" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K492" s="7"/>
       <c r="L492" s="7"/>

--- a/Data/FlightPlan/FPL_20AUG26.xlsx
+++ b/Data/FlightPlan/FPL_20AUG26.xlsx
@@ -299,7 +299,7 @@
     <t>19:50</t>
   </si>
   <si>
-    <t>20:21</t>
+    <t>20:04</t>
   </si>
   <si>
     <t>22:30</t>
@@ -563,15 +563,24 @@
     <t>16:40</t>
   </si>
   <si>
-    <t>19:11</t>
+    <t>19:05</t>
   </si>
   <si>
     <t>20:10</t>
   </si>
   <si>
+    <t>20:50</t>
+  </si>
+  <si>
     <t>20:45</t>
   </si>
   <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
     <t>VN-A535</t>
   </si>
   <si>
@@ -626,9 +635,6 @@
     <t>18:24</t>
   </si>
   <si>
-    <t>21:25</t>
-  </si>
-  <si>
     <t>VN-A539</t>
   </si>
   <si>
@@ -650,9 +656,6 @@
     <t>16:35</t>
   </si>
   <si>
-    <t>19:05</t>
-  </si>
-  <si>
     <t>19:13</t>
   </si>
   <si>
@@ -689,6 +692,9 @@
     <t>19:10</t>
   </si>
   <si>
+    <t>19:17</t>
+  </si>
+  <si>
     <t>19:45</t>
   </si>
   <si>
@@ -764,6 +770,9 @@
     <t>20:35</t>
   </si>
   <si>
+    <t>20:52</t>
+  </si>
+  <si>
     <t>VN-A549</t>
   </si>
   <si>
@@ -857,6 +866,9 @@
     <t>16:37</t>
   </si>
   <si>
+    <t>19:06</t>
+  </si>
+  <si>
     <t>20:30</t>
   </si>
   <si>
@@ -911,15 +923,9 @@
     <t>17:10</t>
   </si>
   <si>
-    <t>20:50</t>
-  </si>
-  <si>
     <t>22:25</t>
   </si>
   <si>
-    <t>22:40</t>
-  </si>
-  <si>
     <t>23:00</t>
   </si>
   <si>
@@ -1004,6 +1010,9 @@
     <t>13:45</t>
   </si>
   <si>
+    <t>19:47</t>
+  </si>
+  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1052,7 +1061,7 @@
     <t>16:38</t>
   </si>
   <si>
-    <t>18:32</t>
+    <t>18:28</t>
   </si>
   <si>
     <t>19:15</t>
@@ -1181,6 +1190,9 @@
     <t>17:51</t>
   </si>
   <si>
+    <t>20:51</t>
+  </si>
+  <si>
     <t>23:05</t>
   </si>
   <si>
@@ -1274,6 +1286,9 @@
     <t>16:23</t>
   </si>
   <si>
+    <t>19:27</t>
+  </si>
+  <si>
     <t>VN-A647</t>
   </si>
   <si>
@@ -1331,6 +1346,9 @@
     <t>14:41</t>
   </si>
   <si>
+    <t>18:41</t>
+  </si>
+  <si>
     <t>VN-A651</t>
   </si>
   <si>
@@ -1481,6 +1499,9 @@
     <t>08:06</t>
   </si>
   <si>
+    <t>20:15</t>
+  </si>
+  <si>
     <t>VN-A668</t>
   </si>
   <si>
@@ -1490,6 +1511,9 @@
     <t>13:44</t>
   </si>
   <si>
+    <t>19:04</t>
+  </si>
+  <si>
     <t>00:20</t>
   </si>
   <si>
@@ -1559,6 +1583,9 @@
     <t>17:40</t>
   </si>
   <si>
+    <t>18:56</t>
+  </si>
+  <si>
     <t>00:25</t>
   </si>
   <si>
@@ -1577,9 +1604,6 @@
     <t>16:02</t>
   </si>
   <si>
-    <t>20:15</t>
-  </si>
-  <si>
     <t>VN-A685</t>
   </si>
   <si>
@@ -1628,6 +1652,9 @@
     <t>ENH</t>
   </si>
   <si>
+    <t>20:01</t>
+  </si>
+  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -1682,7 +1709,7 @@
     <t>MEL</t>
   </si>
   <si>
-    <t>01:45</t>
+    <t>01:32</t>
   </si>
   <si>
     <t>02:50</t>
@@ -1703,9 +1730,6 @@
     <t>KJA</t>
   </si>
   <si>
-    <t>20:52</t>
-  </si>
-  <si>
     <t>05:50</t>
   </si>
   <si>
@@ -1727,7 +1751,7 @@
     <t>Total Record(s): 409</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 20, 2026 17:36</t>
+    <t xml:space="preserve">Generated on  Aug 20, 2026 18:04</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4574,9 +4598,13 @@
       <c t="s" r="J80" s="7">
         <v>185</v>
       </c>
-      <c r="K80" s="7"/>
+      <c t="s" r="K80" s="7">
+        <v>110</v>
+      </c>
       <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
+      <c t="s" r="M80" s="7">
+        <v>186</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
@@ -4602,14 +4630,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="J81" s="7">
         <v>115</v>
       </c>
-      <c r="K81" s="7"/>
+      <c t="s" r="K81" s="7">
+        <v>188</v>
+      </c>
       <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
+      <c t="s" r="M81" s="7">
+        <v>189</v>
+      </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
       <c r="A82" s="6"/>
@@ -4638,7 +4670,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4650,15 +4682,15 @@
         <v>162</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4673,7 +4705,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4688,7 +4720,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4708,7 +4740,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4723,12 +4755,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4743,7 +4775,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4752,18 +4784,18 @@
         <v>162</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
       <c t="s" r="M86" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
     </row>
     <row r="87" ht="14.25" customHeight="1">
@@ -4778,19 +4810,19 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>162</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J87" s="7">
         <v>83</v>
@@ -4811,7 +4843,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4823,10 +4855,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4859,7 +4891,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4874,10 +4906,10 @@
         <v>157</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="K90" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
@@ -4896,7 +4928,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4916,7 +4948,7 @@
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4931,7 +4963,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4946,7 +4978,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4979,7 +5011,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5014,7 +5046,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5026,15 +5058,15 @@
         <v>169</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5049,7 +5081,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5069,7 +5101,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5084,7 +5116,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5096,7 +5128,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J97" s="7">
         <v>68</v>
@@ -5104,7 +5136,7 @@
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5119,7 +5151,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5134,12 +5166,12 @@
         <v>93</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5154,7 +5186,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5166,10 +5198,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5202,7 +5234,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5214,15 +5246,15 @@
         <v>109</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5237,7 +5269,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5246,10 +5278,10 @@
         <v>109</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>122</v>
@@ -5257,7 +5289,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5272,22 +5304,22 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5307,7 +5339,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5319,14 +5351,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>227</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
@@ -5340,7 +5374,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5352,7 +5386,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>113</v>
@@ -5373,7 +5407,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5385,10 +5419,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5421,7 +5455,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5430,7 +5464,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I108" s="7">
         <v>170</v>
@@ -5441,7 +5475,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5456,13 +5490,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>16</v>
@@ -5476,7 +5510,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5491,7 +5525,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5500,20 +5534,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I110" s="7">
         <v>46</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="K110" s="7">
         <v>46</v>
       </c>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5528,27 +5562,27 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5563,7 +5597,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5572,10 +5606,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>85</v>
@@ -5596,22 +5630,22 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5644,7 +5678,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5659,12 +5693,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5679,7 +5713,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5694,12 +5728,12 @@
         <v>181</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5714,7 +5748,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5726,10 +5760,10 @@
         <v>156</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5747,7 +5781,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5759,7 +5793,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J118" s="7">
         <v>71</v>
@@ -5795,7 +5829,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5807,10 +5841,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5830,7 +5864,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5842,15 +5876,15 @@
         <v>118</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
       <c t="s" r="M121" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="122" ht="14.25" customHeight="1">
@@ -5865,7 +5899,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5877,14 +5911,16 @@
         <v>26</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
+      <c t="s" r="M122" s="7">
+        <v>253</v>
+      </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c r="A123" s="6"/>
@@ -5913,7 +5949,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5925,7 +5961,7 @@
         <v>172</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>119</v>
@@ -5933,7 +5969,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5948,7 +5984,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5963,12 +5999,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5983,7 +6019,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5995,7 +6031,7 @@
         <v>91</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J126" s="7">
         <v>179</v>
@@ -6003,7 +6039,7 @@
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6018,7 +6054,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -6053,7 +6089,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6062,13 +6098,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="I128" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -6086,22 +6122,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -6134,7 +6170,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6146,15 +6182,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6169,7 +6205,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6204,7 +6240,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -6224,7 +6260,7 @@
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c t="s" r="M133" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="134" ht="14.25" customHeight="1">
@@ -6239,7 +6275,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6254,14 +6290,14 @@
         <v>161</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="K134" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6276,7 +6312,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6291,14 +6327,14 @@
         <v>46</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="K135" s="7">
         <v>22</v>
       </c>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6313,7 +6349,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6325,10 +6361,10 @@
         <v>109</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="K136" s="7">
         <v>68</v>
@@ -6350,7 +6386,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6365,14 +6401,14 @@
         <v>48</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="K137" s="7">
         <v>107</v>
       </c>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6387,7 +6423,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6402,14 +6438,14 @@
         <v>153</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c t="s" r="K138" s="7">
         <v>143</v>
       </c>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6424,7 +6460,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6439,14 +6475,14 @@
         <v>154</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="K139" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6476,7 +6512,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6496,7 +6532,7 @@
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6511,7 +6547,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6526,12 +6562,12 @@
         <v>140</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6546,7 +6582,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6555,13 +6591,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="I143" s="7">
         <v>110</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6579,22 +6615,22 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6627,7 +6663,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6642,12 +6678,12 @@
         <v>64</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6662,7 +6698,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6677,12 +6713,12 @@
         <v>106</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6697,7 +6733,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6709,14 +6745,16 @@
         <v>41</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c r="M148" s="7"/>
+      <c t="s" r="M148" s="7">
+        <v>285</v>
+      </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
@@ -6730,7 +6768,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6745,7 +6783,7 @@
         <v>153</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6774,11 +6812,11 @@
         <v>2987</v>
       </c>
       <c t="s" r="C151" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6790,17 +6828,17 @@
         <v>109</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="K151" s="7">
         <v>173</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6815,7 +6853,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6827,7 +6865,7 @@
         <v>132</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J152" s="7">
         <v>120</v>
@@ -6837,7 +6875,7 @@
       </c>
       <c r="L152" s="7"/>
       <c t="s" r="M152" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
@@ -6852,7 +6890,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6874,7 +6912,7 @@
       </c>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6889,7 +6927,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6901,7 +6939,7 @@
         <v>41</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="J154" s="7">
         <v>61</v>
@@ -6909,7 +6947,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6924,7 +6962,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6944,7 +6982,7 @@
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6959,7 +6997,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6974,7 +7012,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6992,7 +7030,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7001,13 +7039,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -7040,7 +7078,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7075,7 +7113,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7095,7 +7133,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7110,7 +7148,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7122,7 +7160,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>51</v>
@@ -7147,7 +7185,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7165,11 +7203,11 @@
         <v>115</v>
       </c>
       <c t="s" r="K162" s="7">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7184,7 +7222,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -7196,17 +7234,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c t="s" r="J163" s="7">
         <v>73</v>
       </c>
       <c t="s" r="K163" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -7221,7 +7259,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7233,10 +7271,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -7265,11 +7303,11 @@
         <v>7621</v>
       </c>
       <c t="s" r="C166" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -7281,15 +7319,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7304,7 +7342,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7313,13 +7351,13 @@
         <v>135</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="I167" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7337,19 +7375,19 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c t="s" r="H168" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>144</v>
@@ -7370,7 +7408,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7382,7 +7420,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>150</v>
@@ -7418,7 +7456,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7433,12 +7471,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7453,7 +7491,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7465,15 +7503,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7488,7 +7526,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7497,13 +7535,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7521,13 +7559,13 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>16</v>
@@ -7536,7 +7574,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7569,7 +7607,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7581,15 +7619,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7604,7 +7642,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7613,7 +7651,7 @@
         <v>135</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="I177" s="7">
         <v>60</v>
@@ -7624,7 +7662,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7639,13 +7677,13 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>135</v>
@@ -7668,11 +7706,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C179" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7684,7 +7722,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>138</v>
@@ -7701,11 +7739,11 @@
         <v>7614</v>
       </c>
       <c t="s" r="C180" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7714,10 +7752,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>45</v>
@@ -7753,7 +7791,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7765,15 +7803,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7788,7 +7826,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7797,18 +7835,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7823,13 +7861,13 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
@@ -7858,7 +7896,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7870,7 +7908,7 @@
         <v>172</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>153</v>
@@ -7895,7 +7933,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7917,7 +7955,7 @@
       </c>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7947,7 +7985,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7967,7 +8005,7 @@
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7982,7 +8020,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -8002,7 +8040,7 @@
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
       <c t="s" r="M189" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1">
@@ -8017,7 +8055,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8052,7 +8090,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8061,20 +8099,20 @@
         <v>109</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>92</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="K191" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8089,13 +8127,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>16</v>
@@ -8108,7 +8146,9 @@
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
-      <c r="M192" s="7"/>
+      <c t="s" r="M192" s="7">
+        <v>333</v>
+      </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
       <c t="s" r="A193" s="6">
@@ -8122,7 +8162,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -8131,10 +8171,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>99</v>
@@ -8155,22 +8195,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8203,7 +8243,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8215,15 +8255,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8238,7 +8278,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8258,7 +8298,7 @@
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8273,7 +8313,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8308,7 +8348,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8320,15 +8360,15 @@
         <v>77</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8343,7 +8383,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8391,7 +8431,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8403,7 +8443,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>86</v>
@@ -8426,7 +8466,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8435,18 +8475,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8461,27 +8501,27 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8496,7 +8536,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8511,14 +8551,14 @@
         <v>60</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="K205" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8533,7 +8573,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8555,7 +8595,7 @@
       </c>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8570,7 +8610,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8588,11 +8628,11 @@
         <v>34</v>
       </c>
       <c t="s" r="K207" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8607,7 +8647,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8619,7 +8659,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>116</v>
@@ -8629,7 +8669,7 @@
       </c>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8659,7 +8699,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8671,7 +8711,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>90</v>
@@ -8679,7 +8719,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8694,7 +8734,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8706,15 +8746,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8729,7 +8769,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8738,13 +8778,13 @@
         <v>135</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>80</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8764,13 +8804,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>135</v>
@@ -8779,7 +8819,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8797,7 +8837,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8809,10 +8849,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8845,7 +8885,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8857,15 +8897,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8880,7 +8920,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8892,15 +8932,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8915,7 +8955,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8930,12 +8970,12 @@
         <v>131</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8950,7 +8990,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8959,10 +8999,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>80</v>
@@ -8970,7 +9010,7 @@
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8985,13 +9025,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>26</v>
@@ -9000,11 +9040,13 @@
         <v>70</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
-      <c r="M220" s="7"/>
+      <c t="s" r="M220" s="7">
+        <v>184</v>
+      </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
       <c t="s" r="A221" s="6">
@@ -9018,7 +9060,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9033,11 +9075,15 @@
         <v>82</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>365</v>
-      </c>
-      <c r="K221" s="7"/>
+        <v>368</v>
+      </c>
+      <c t="s" r="K221" s="7">
+        <v>110</v>
+      </c>
       <c r="L221" s="7"/>
-      <c r="M221" s="7"/>
+      <c t="s" r="M221" s="7">
+        <v>53</v>
+      </c>
     </row>
     <row r="222" ht="14.25" customHeight="1">
       <c r="A222" s="6"/>
@@ -9066,7 +9112,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9078,10 +9124,10 @@
         <v>162</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -9101,7 +9147,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9110,18 +9156,18 @@
         <v>162</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="I224" s="7">
         <v>90</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9136,27 +9182,27 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>162</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9171,7 +9217,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9204,7 +9250,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9216,10 +9262,10 @@
         <v>109</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -9252,7 +9298,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9287,7 +9333,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9299,7 +9345,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>92</v>
@@ -9307,7 +9353,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9322,7 +9368,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9331,7 +9377,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I231" s="7">
         <v>133</v>
@@ -9357,22 +9403,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -9392,7 +9438,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9440,7 +9486,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9452,7 +9498,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c t="s" r="J235" s="7">
         <v>148</v>
@@ -9460,7 +9506,7 @@
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9475,7 +9521,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9487,7 +9533,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>159</v>
@@ -9495,7 +9541,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9510,7 +9556,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9522,7 +9568,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>46</v>
@@ -9530,7 +9576,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9545,7 +9591,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9557,15 +9603,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9580,7 +9626,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9589,18 +9635,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>183</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9615,13 +9661,13 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>16</v>
@@ -9630,7 +9676,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9648,7 +9694,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9657,13 +9703,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9681,22 +9727,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9729,7 +9775,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9738,10 +9784,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>159</v>
@@ -9764,22 +9810,22 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9799,7 +9845,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9808,10 +9854,10 @@
         <v>109</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J246" s="7">
         <v>182</v>
@@ -9819,7 +9865,7 @@
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9834,26 +9880,28 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
-      <c r="M247" s="7"/>
+      <c t="s" r="M247" s="7">
+        <v>393</v>
+      </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
       <c t="s" r="A248" s="6">
@@ -9863,11 +9911,11 @@
         <v>8020</v>
       </c>
       <c t="s" r="C248" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9876,13 +9924,13 @@
         <v>109</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9896,26 +9944,26 @@
         <v>8021</v>
       </c>
       <c t="s" r="C249" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9948,7 +9996,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9957,7 +10005,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H251" s="8">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="I251" s="7">
         <v>67</v>
@@ -9968,7 +10016,7 @@
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9983,13 +10031,13 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>16</v>
@@ -9998,12 +10046,12 @@
         <v>179</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10018,7 +10066,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10027,20 +10075,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>68</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c t="s" r="K253" s="7">
         <v>48</v>
       </c>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10055,29 +10103,29 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="K254" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>205</v>
+        <v>188</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10107,7 +10155,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10116,18 +10164,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10142,13 +10190,13 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>26</v>
@@ -10162,7 +10210,7 @@
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10177,7 +10225,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10197,7 +10245,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10212,7 +10260,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10224,7 +10272,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>142</v>
@@ -10232,7 +10280,7 @@
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10247,7 +10295,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10262,12 +10310,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>167</v>
+        <v>33</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10282,7 +10330,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10294,10 +10342,10 @@
         <v>109</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -10315,7 +10363,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10327,10 +10375,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10363,7 +10411,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10375,15 +10423,15 @@
         <v>109</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10398,7 +10446,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10418,7 +10466,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10433,7 +10481,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -10442,20 +10490,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I266" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="K266" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10470,25 +10518,25 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>89</v>
       </c>
       <c t="s" r="K267" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
@@ -10507,7 +10555,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10519,13 +10567,13 @@
         <v>135</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>59</v>
       </c>
       <c t="s" r="K268" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
@@ -10544,7 +10592,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10556,17 +10604,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="K269" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10581,7 +10629,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10596,14 +10644,14 @@
         <v>165</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c t="s" r="K270" s="7">
         <v>81</v>
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10618,7 +10666,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10630,17 +10678,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>34</v>
       </c>
       <c t="s" r="K271" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10655,7 +10703,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10667,10 +10715,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10703,7 +10751,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10715,15 +10763,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10738,7 +10786,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10747,10 +10795,10 @@
         <v>135</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="J275" s="7">
         <v>93</v>
@@ -10758,7 +10806,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10773,13 +10821,13 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>135</v>
@@ -10793,7 +10841,7 @@
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10808,7 +10856,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10823,7 +10871,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10841,7 +10889,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10853,10 +10901,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10889,27 +10937,27 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10924,7 +10972,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10933,17 +10981,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>167</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
-      <c r="M281" s="7"/>
+      <c t="s" r="M281" s="7">
+        <v>425</v>
+      </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
       <c t="s" r="A282" s="6">
@@ -10957,13 +11007,13 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F282" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>16</v>
@@ -10972,7 +11022,7 @@
         <v>83</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10990,7 +11040,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -11038,7 +11088,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -11058,7 +11108,7 @@
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11073,7 +11123,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -11085,15 +11135,15 @@
         <v>109</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11108,7 +11158,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11123,7 +11173,7 @@
         <v>151</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -11143,7 +11193,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11158,14 +11208,14 @@
         <v>104</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c t="s" r="K288" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -11180,7 +11230,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -11195,14 +11245,14 @@
         <v>122</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="K289" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="L289" s="7"/>
       <c t="s" r="M289" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="290" ht="15" customHeight="1">
@@ -11217,7 +11267,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11229,17 +11279,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>82</v>
       </c>
       <c t="s" r="K290" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11269,7 +11319,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11281,7 +11331,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>119</v>
@@ -11304,7 +11354,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11319,12 +11369,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11339,7 +11389,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11351,15 +11401,15 @@
         <v>135</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11389,7 +11439,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11398,18 +11448,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11424,19 +11474,19 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J297" s="7">
         <v>86</v>
@@ -11444,7 +11494,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11459,7 +11509,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
@@ -11468,7 +11518,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="I298" s="7">
         <v>88</v>
@@ -11479,7 +11529,7 @@
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11494,13 +11544,13 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>16</v>
@@ -11514,7 +11564,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11529,7 +11579,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
@@ -11538,18 +11588,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11564,22 +11614,22 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F301" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11599,7 +11649,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F302" s="7">
         <v>320</v>
@@ -11608,20 +11658,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>165</v>
       </c>
       <c t="s" r="K302" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>427</v>
+        <v>445</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11636,13 +11686,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="F303" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>16</v>
@@ -11654,7 +11704,7 @@
         <v>51</v>
       </c>
       <c t="s" r="K303" s="7">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
@@ -11688,7 +11738,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11700,15 +11750,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11723,7 +11773,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
@@ -11732,10 +11782,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>21</v>
@@ -11743,7 +11793,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11758,13 +11808,13 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>16</v>
@@ -11778,7 +11828,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11808,7 +11858,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11823,12 +11873,12 @@
         <v>119</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11843,7 +11893,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11855,7 +11905,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J310" s="7">
         <v>89</v>
@@ -11878,7 +11928,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F311" s="7">
         <v>321</v>
@@ -11887,7 +11937,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I311" s="7">
         <v>178</v>
@@ -11898,7 +11948,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11913,19 +11963,19 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>182</v>
@@ -11946,7 +11996,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11958,10 +12008,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11994,7 +12044,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -12003,18 +12053,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12029,19 +12079,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>104</v>
@@ -12049,7 +12099,7 @@
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12064,7 +12114,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -12076,7 +12126,7 @@
         <v>132</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>140</v>
@@ -12084,7 +12134,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -12099,7 +12149,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12111,7 +12161,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>80</v>
@@ -12119,7 +12169,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12134,7 +12184,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12143,20 +12193,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H319" s="8">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c t="s" r="I319" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="K319" s="7">
         <v>167</v>
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12171,22 +12221,22 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G320" s="8">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c t="s" r="H320" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -12219,7 +12269,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -12234,12 +12284,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12254,7 +12304,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12266,10 +12316,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -12289,7 +12339,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -12301,17 +12351,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c t="s" r="K324" s="7">
         <v>89</v>
       </c>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12326,7 +12376,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12335,7 +12385,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>181</v>
@@ -12346,7 +12396,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12361,22 +12411,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12409,7 +12459,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -12418,18 +12468,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12444,13 +12494,13 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H329" s="8">
         <v>41</v>
@@ -12459,12 +12509,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>460</v>
+        <v>466</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12479,7 +12529,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -12488,18 +12538,18 @@
         <v>41</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12514,22 +12564,22 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12562,7 +12612,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -12571,10 +12621,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>131</v>
@@ -12582,7 +12632,7 @@
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12597,13 +12647,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>26</v>
@@ -12612,12 +12662,12 @@
         <v>92</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12632,7 +12682,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12641,18 +12691,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I335" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12667,13 +12717,13 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>26</v>
@@ -12682,7 +12732,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -12711,11 +12761,11 @@
         <v>39</v>
       </c>
       <c t="s" r="C338" s="7">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12727,7 +12777,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>92</v>
@@ -12735,7 +12785,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12750,7 +12800,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12762,17 +12812,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="K339" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12802,7 +12852,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12814,7 +12864,7 @@
         <v>172</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>44</v>
@@ -12837,7 +12887,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12849,15 +12899,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12872,7 +12922,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12884,15 +12934,15 @@
         <v>172</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12907,7 +12957,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12919,7 +12969,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>179</v>
@@ -12927,7 +12977,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12942,7 +12992,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12951,10 +13001,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>165</v>
@@ -12962,7 +13012,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12977,13 +13027,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>26</v>
@@ -13025,7 +13075,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13034,10 +13084,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>174</v>
@@ -13045,7 +13095,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13060,13 +13110,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>26</v>
@@ -13080,7 +13130,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13095,7 +13145,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13107,15 +13157,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13130,7 +13180,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13142,15 +13192,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -13165,7 +13215,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13180,12 +13230,12 @@
         <v>70</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -13200,7 +13250,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -13212,7 +13262,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>113</v>
@@ -13248,7 +13298,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13257,18 +13307,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13283,22 +13333,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13318,7 +13368,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -13327,7 +13377,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I357" s="7">
         <v>18</v>
@@ -13338,7 +13388,7 @@
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -13353,19 +13403,19 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>78</v>
@@ -13388,7 +13438,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -13397,13 +13447,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c t="s" r="I359" s="7">
         <v>62</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -13421,19 +13471,19 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>147</v>
@@ -13469,7 +13519,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13481,15 +13531,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13504,7 +13554,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -13539,7 +13589,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13551,7 +13601,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c t="s" r="J364" s="7">
         <v>30</v>
@@ -13574,7 +13624,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13583,13 +13633,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13609,26 +13659,28 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
-      <c r="M366" s="7"/>
+      <c t="s" r="M366" s="7">
+        <v>496</v>
+      </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
       <c t="s" r="A367" s="6">
@@ -13642,7 +13694,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13657,7 +13709,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13690,19 +13742,19 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>106</v>
@@ -13710,7 +13762,7 @@
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13725,7 +13777,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13734,7 +13786,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H370" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="I370" s="7">
         <v>60</v>
@@ -13745,7 +13797,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13760,26 +13812,28 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G371" s="8">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="H371" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>167</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
-      <c r="M371" s="7"/>
+      <c t="s" r="M371" s="7">
+        <v>500</v>
+      </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
       <c t="s" r="A372" s="6">
@@ -13793,7 +13847,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13802,13 +13856,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13826,13 +13880,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>26</v>
@@ -13841,7 +13895,7 @@
         <v>144</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13874,7 +13928,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13886,15 +13940,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>496</v>
+        <v>504</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13909,7 +13963,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13924,12 +13978,12 @@
         <v>28</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13944,7 +13998,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13964,7 +14018,7 @@
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -13979,7 +14033,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -14012,7 +14066,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14024,10 +14078,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -14060,7 +14114,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -14080,7 +14134,7 @@
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
-        <v>499</v>
+        <v>507</v>
       </c>
     </row>
     <row r="382" ht="14.25" customHeight="1">
@@ -14095,7 +14149,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14104,10 +14158,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>178</v>
@@ -14115,7 +14169,7 @@
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14130,19 +14184,19 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>142</v>
@@ -14165,7 +14219,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14187,7 +14241,7 @@
       </c>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14202,7 +14256,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14214,7 +14268,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c t="s" r="J385" s="7">
         <v>114</v>
@@ -14235,7 +14289,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14247,10 +14301,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -14283,7 +14337,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14292,18 +14346,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>501</v>
+        <v>509</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14318,19 +14372,19 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>18</v>
@@ -14338,7 +14392,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14353,7 +14407,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14365,15 +14419,15 @@
         <v>162</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>503</v>
+        <v>511</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14388,7 +14442,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -14408,7 +14462,7 @@
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>504</v>
+        <v>512</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14423,7 +14477,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14432,7 +14486,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>164</v>
@@ -14443,7 +14497,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -14458,13 +14512,13 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
@@ -14473,7 +14527,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14491,7 +14545,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
@@ -14503,10 +14557,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14539,7 +14593,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -14551,7 +14605,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>18</v>
@@ -14559,7 +14613,7 @@
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14574,7 +14628,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14589,12 +14643,12 @@
         <v>129</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>506</v>
+        <v>514</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -14609,7 +14663,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14621,17 +14675,17 @@
         <v>41</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="K398" s="7">
         <v>90</v>
       </c>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14646,7 +14700,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
@@ -14661,14 +14715,14 @@
         <v>179</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="K399" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>507</v>
+        <v>515</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14683,7 +14737,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -14695,17 +14749,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="K400" s="7">
         <v>165</v>
       </c>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14735,7 +14789,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14747,15 +14801,15 @@
         <v>41</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14770,7 +14824,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14782,7 +14836,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>161</v>
@@ -14790,7 +14844,7 @@
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
       <c t="s" r="M403" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="404" ht="14.25" customHeight="1">
@@ -14805,7 +14859,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14814,10 +14868,10 @@
         <v>109</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>122</v>
@@ -14825,7 +14879,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>510</v>
+        <v>518</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14840,13 +14894,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>109</v>
@@ -14855,12 +14909,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14875,7 +14929,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14884,13 +14938,13 @@
         <v>109</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14908,22 +14962,22 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>109</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>302</v>
+        <v>189</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -14941,7 +14995,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14956,7 +15010,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14989,7 +15043,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F410" s="7">
         <v>320</v>
@@ -14998,18 +15052,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>512</v>
+        <v>520</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15024,13 +15078,13 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F411" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>26</v>
@@ -15044,7 +15098,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -15059,7 +15113,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -15068,10 +15122,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>131</v>
@@ -15079,7 +15133,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>513</v>
+        <v>521</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15094,13 +15148,13 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>26</v>
@@ -15109,12 +15163,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15129,7 +15183,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15138,18 +15192,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>61</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15164,26 +15218,28 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>82</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
-      <c r="M415" s="7"/>
+      <c t="s" r="M415" s="7">
+        <v>524</v>
+      </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
       <c t="s" r="A416" s="6">
@@ -15197,7 +15253,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15209,10 +15265,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -15230,7 +15286,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15245,7 +15301,7 @@
         <v>137</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -15278,7 +15334,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -15290,7 +15346,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>157</v>
@@ -15298,7 +15354,7 @@
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15313,7 +15369,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -15325,7 +15381,7 @@
         <v>102</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>131</v>
@@ -15333,7 +15389,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>518</v>
+        <v>527</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15348,7 +15404,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F421" s="7">
         <v>321</v>
@@ -15368,7 +15424,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>519</v>
+        <v>528</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15383,7 +15439,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F422" s="7">
         <v>321</v>
@@ -15392,10 +15448,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>110</v>
@@ -15405,7 +15461,7 @@
       </c>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15420,13 +15476,13 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F423" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>16</v>
@@ -15438,11 +15494,11 @@
         <v>115</v>
       </c>
       <c t="s" r="K423" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15472,7 +15528,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F425" s="7">
         <v>321</v>
@@ -15492,7 +15548,7 @@
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
       <c t="s" r="M425" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="426" ht="14.25" customHeight="1">
@@ -15507,7 +15563,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F426" s="7">
         <v>321</v>
@@ -15519,7 +15575,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>78</v>
@@ -15527,7 +15583,7 @@
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
       <c t="s" r="M426" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="427" ht="14.25" customHeight="1">
@@ -15542,7 +15598,7 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F427" s="7">
         <v>321</v>
@@ -15554,7 +15610,7 @@
         <v>162</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c t="s" r="J427" s="7">
         <v>61</v>
@@ -15562,7 +15618,7 @@
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
       <c t="s" r="M427" s="7">
-        <v>521</v>
+        <v>530</v>
       </c>
     </row>
     <row r="428" ht="14.25" customHeight="1">
@@ -15577,7 +15633,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15592,11 +15648,13 @@
         <v>68</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
-      <c r="M428" s="7"/>
+      <c t="s" r="M428" s="7">
+        <v>248</v>
+      </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
       <c t="s" r="A429" s="6">
@@ -15610,7 +15668,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15619,7 +15677,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H429" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I429" s="7">
         <v>31</v>
@@ -15628,11 +15686,11 @@
         <v>153</v>
       </c>
       <c t="s" r="K429" s="7">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>522</v>
+        <v>269</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15647,13 +15705,13 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G430" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H430" s="8">
         <v>16</v>
@@ -15662,14 +15720,14 @@
         <v>83</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c t="s" r="K430" s="7">
-        <v>300</v>
+        <v>407</v>
       </c>
       <c r="L430" s="7"/>
       <c t="s" r="M430" s="7">
-        <v>453</v>
+        <v>261</v>
       </c>
     </row>
     <row r="431" ht="14.25" customHeight="1">
@@ -15699,27 +15757,27 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G432" s="8">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c t="s" r="H432" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
       <c t="s" r="M432" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="433" ht="14.25" customHeight="1">
@@ -15734,7 +15792,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -15754,7 +15812,7 @@
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
       <c t="s" r="M433" s="7">
-        <v>525</v>
+        <v>533</v>
       </c>
     </row>
     <row r="434" ht="14.25" customHeight="1">
@@ -15769,7 +15827,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15784,7 +15842,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -15804,7 +15862,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15816,17 +15874,17 @@
         <v>135</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c t="s" r="J435" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="K435" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>526</v>
+        <v>534</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15841,7 +15899,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -15863,7 +15921,7 @@
       </c>
       <c r="L436" s="7"/>
       <c t="s" r="M436" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="437" ht="14.25" customHeight="1">
@@ -15878,7 +15936,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>523</v>
+        <v>531</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15887,10 +15945,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>527</v>
+        <v>535</v>
       </c>
       <c t="s" r="J437" s="7">
         <v>64</v>
@@ -15926,7 +15984,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15941,12 +15999,12 @@
         <v>147</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15961,7 +16019,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15976,12 +16034,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J440" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>529</v>
+        <v>537</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15996,7 +16054,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -16005,13 +16063,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H441" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -16031,13 +16089,13 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G442" s="8">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c t="s" r="H442" s="8">
         <v>16</v>
@@ -16046,12 +16104,12 @@
         <v>22</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K442" s="7"/>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -16066,7 +16124,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -16075,7 +16133,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H443" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I443" s="7">
         <v>181</v>
@@ -16088,7 +16146,7 @@
       </c>
       <c r="L443" s="7"/>
       <c t="s" r="M443" s="7">
-        <v>530</v>
+        <v>538</v>
       </c>
     </row>
     <row r="444" ht="14.25" customHeight="1">
@@ -16103,13 +16161,13 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G444" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H444" s="8">
         <v>16</v>
@@ -16125,7 +16183,7 @@
       </c>
       <c r="L444" s="7"/>
       <c t="s" r="M444" s="7">
-        <v>522</v>
+        <v>496</v>
       </c>
     </row>
     <row r="445" ht="15" customHeight="1">
@@ -16140,7 +16198,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -16152,13 +16210,13 @@
         <v>162</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>137</v>
       </c>
       <c t="s" r="K445" s="7">
-        <v>300</v>
+        <v>186</v>
       </c>
       <c r="L445" s="7"/>
       <c t="s" r="M445" s="7">
@@ -16177,7 +16235,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>528</v>
+        <v>536</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16189,13 +16247,13 @@
         <v>16</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="J446" s="7">
-        <v>531</v>
+        <v>539</v>
       </c>
       <c t="s" r="K446" s="7">
-        <v>532</v>
+        <v>540</v>
       </c>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
@@ -16229,7 +16287,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F448" s="7">
         <v>320</v>
@@ -16241,7 +16299,7 @@
         <v>135</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>534</v>
+        <v>542</v>
       </c>
       <c t="s" r="J448" s="7">
         <v>43</v>
@@ -16249,7 +16307,7 @@
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>535</v>
+        <v>543</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16264,7 +16322,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F449" s="7">
         <v>320</v>
@@ -16276,15 +16334,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16299,7 +16357,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F450" s="7">
         <v>320</v>
@@ -16308,18 +16366,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H450" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="I450" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c t="s" r="J450" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="K450" s="7"/>
       <c r="L450" s="7"/>
       <c t="s" r="M450" s="7">
-        <v>536</v>
+        <v>544</v>
       </c>
     </row>
     <row r="451" ht="14.25" customHeight="1">
@@ -16334,19 +16392,19 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F451" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G451" s="8">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c t="s" r="H451" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>92</v>
@@ -16354,7 +16412,7 @@
       <c r="K451" s="7"/>
       <c r="L451" s="7"/>
       <c t="s" r="M451" s="7">
-        <v>537</v>
+        <v>545</v>
       </c>
     </row>
     <row r="452" ht="14.25" customHeight="1">
@@ -16369,7 +16427,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F452" s="7">
         <v>320</v>
@@ -16378,7 +16436,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>179</v>
@@ -16404,26 +16462,28 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F453" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>538</v>
+        <v>546</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>83</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
-      <c r="M453" s="7"/>
+      <c t="s" r="M453" s="7">
+        <v>547</v>
+      </c>
     </row>
     <row r="454" ht="14.25" customHeight="1">
       <c t="s" r="A454" s="6">
@@ -16437,7 +16497,7 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F454" s="7">
         <v>320</v>
@@ -16446,13 +16506,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H454" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I454" s="7">
         <v>154</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -16470,22 +16530,22 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>533</v>
+        <v>541</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G455" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H455" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I455" s="7">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -16518,7 +16578,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="F457" s="7">
         <v>321</v>
@@ -16530,15 +16590,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>543</v>
+        <v>552</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16553,7 +16613,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="F458" s="7">
         <v>321</v>
@@ -16562,18 +16622,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
       <c t="s" r="M458" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="459" ht="14.25" customHeight="1">
@@ -16588,19 +16648,19 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="F459" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I459" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c t="s" r="J459" s="7">
         <v>165</v>
@@ -16608,7 +16668,7 @@
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
       <c t="s" r="M459" s="7">
-        <v>508</v>
+        <v>516</v>
       </c>
     </row>
     <row r="460" ht="15" customHeight="1">
@@ -16623,7 +16683,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="F460" s="7">
         <v>321</v>
@@ -16632,20 +16692,20 @@
         <v>26</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c t="s" r="I460" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="K460" s="7">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="L460" s="7"/>
       <c t="s" r="M460" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="461" ht="14.25" customHeight="1">
@@ -16660,22 +16720,22 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="F461" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -16708,7 +16768,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16720,15 +16780,15 @@
         <v>109</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16743,7 +16803,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -16778,7 +16838,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16790,7 +16850,7 @@
         <v>109</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J465" s="7">
         <v>61</v>
@@ -16813,7 +16873,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -16831,11 +16891,11 @@
         <v>31</v>
       </c>
       <c t="s" r="K466" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L466" s="7"/>
       <c t="s" r="M466" s="7">
-        <v>547</v>
+        <v>556</v>
       </c>
     </row>
     <row r="467" ht="14.25" customHeight="1">
@@ -16865,7 +16925,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F468" s="7">
         <v>320</v>
@@ -16874,18 +16934,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H468" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="I468" s="7">
         <v>148</v>
       </c>
       <c t="s" r="J468" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K468" s="7"/>
       <c r="L468" s="7"/>
       <c t="s" r="M468" s="7">
-        <v>549</v>
+        <v>558</v>
       </c>
     </row>
     <row r="469" ht="14.25" customHeight="1">
@@ -16900,19 +16960,19 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F469" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G469" s="8">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c t="s" r="H469" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>20</v>
@@ -16920,7 +16980,7 @@
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
       <c t="s" r="M469" s="7">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -16935,7 +16995,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F470" s="7">
         <v>320</v>
@@ -16944,18 +17004,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H470" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
       <c t="s" r="M470" s="7">
-        <v>550</v>
+        <v>559</v>
       </c>
     </row>
     <row r="471" ht="14.25" customHeight="1">
@@ -16970,22 +17030,22 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F471" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G471" s="8">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="H471" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -17005,7 +17065,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -17017,7 +17077,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I472" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J472" s="7">
         <v>51</v>
@@ -17038,7 +17098,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
@@ -17053,7 +17113,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J473" s="7">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
@@ -17086,13 +17146,13 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="F475" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G475" s="8">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c t="s" r="H475" s="8">
         <v>16</v>
@@ -17101,12 +17161,12 @@
         <v>159</v>
       </c>
       <c t="s" r="J475" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="K475" s="7"/>
       <c r="L475" s="7"/>
       <c t="s" r="M475" s="7">
-        <v>554</v>
+        <v>563</v>
       </c>
     </row>
     <row r="476" ht="14.25" customHeight="1">
@@ -17121,7 +17181,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="F476" s="7">
         <v>330</v>
@@ -17130,7 +17190,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H476" s="8">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c t="s" r="I476" s="7">
         <v>83</v>
@@ -17169,7 +17229,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -17187,7 +17247,7 @@
         <v>150</v>
       </c>
       <c t="s" r="K478" s="7">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="L478" s="7"/>
       <c t="s" r="M478" s="7">
@@ -17206,7 +17266,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -17215,20 +17275,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c t="s" r="I479" s="7">
         <v>20</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c t="s" r="K479" s="7">
         <v>28</v>
       </c>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17243,13 +17303,13 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>16</v>
@@ -17258,14 +17318,14 @@
         <v>73</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c t="s" r="K480" s="7">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17295,7 +17355,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -17304,7 +17364,7 @@
         <v>135</v>
       </c>
       <c t="s" r="H482" s="8">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c t="s" r="I482" s="7">
         <v>38</v>
@@ -17315,7 +17375,7 @@
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
       <c t="s" r="M482" s="7">
-        <v>561</v>
+        <v>570</v>
       </c>
     </row>
     <row r="483" ht="14.25" customHeight="1">
@@ -17330,22 +17390,22 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G483" s="8">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c t="s" r="H483" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c t="s" r="J483" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
@@ -17378,7 +17438,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="F485" s="7">
         <v>330</v>
@@ -17393,12 +17453,12 @@
         <v>151</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
       <c t="s" r="M485" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="486" ht="14.25" customHeight="1">
@@ -17413,7 +17473,7 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
@@ -17422,10 +17482,10 @@
         <v>135</v>
       </c>
       <c t="s" r="H486" s="8">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>34</v>
@@ -17433,7 +17493,7 @@
       <c r="K486" s="7"/>
       <c r="L486" s="7"/>
       <c t="s" r="M486" s="7">
-        <v>564</v>
+        <v>253</v>
       </c>
     </row>
     <row r="487" ht="14.25" customHeight="1">
@@ -17448,22 +17508,22 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="F487" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G487" s="8">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c t="s" r="H487" s="8">
         <v>135</v>
       </c>
       <c t="s" r="I487" s="7">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c t="s" r="J487" s="7">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
@@ -17496,7 +17556,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
@@ -17511,12 +17571,12 @@
         <v>129</v>
       </c>
       <c t="s" r="J489" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="K489" s="7"/>
       <c r="L489" s="7"/>
       <c t="s" r="M489" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="490" ht="15" customHeight="1">
@@ -17531,7 +17591,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
@@ -17540,7 +17600,7 @@
         <v>135</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c t="s" r="I490" s="7">
         <v>131</v>
@@ -17566,13 +17626,13 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>566</v>
+        <v>574</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>567</v>
+        <v>575</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>135</v>
@@ -17581,7 +17641,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -17614,7 +17674,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="F493" s="7">
         <v>330</v>
@@ -17623,7 +17683,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H493" s="8">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c t="s" r="I493" s="7">
         <v>159</v>
@@ -17649,19 +17709,19 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>568</v>
+        <v>576</v>
       </c>
       <c r="F494" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G494" s="8">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c t="s" r="H494" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c t="s" r="J494" s="7">
         <v>147</v>
@@ -17672,7 +17732,7 @@
     </row>
     <row r="495" ht="16.5" customHeight="1">
       <c t="s" r="A495" s="9">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="B495" s="9"/>
       <c r="C495" s="9"/>
@@ -17692,7 +17752,7 @@
     <row r="496" ht="65.25" customHeight="1"/>
     <row r="497" ht="16.5" customHeight="1">
       <c t="s" r="A497" s="10">
-        <v>572</v>
+        <v>580</v>
       </c>
       <c r="B497" s="10"/>
       <c r="C497" s="10"/>
@@ -17705,7 +17765,7 @@
       <c r="J497" s="10"/>
       <c r="K497" s="10"/>
       <c t="s" r="L497" s="11">
-        <v>573</v>
+        <v>581</v>
       </c>
       <c r="M497" s="11"/>
       <c r="N497" s="11"/>
